--- a/Cplusplus/04. MEMORY MANAGEMENT.xlsx
+++ b/Cplusplus/04. MEMORY MANAGEMENT.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="CheckList C++" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="784">
   <si>
     <t>[ ] Function pointers</t>
   </si>
@@ -1352,180 +1352,21 @@
     <t>Smart Pointers (C++11)</t>
   </si>
   <si>
-    <t>std::unique_ptr</t>
-  </si>
-  <si>
-    <t>#include &lt;memory&gt;</t>
-  </si>
-  <si>
-    <t>// Tạo unique_ptr</t>
-  </si>
-  <si>
-    <t>std::unique_ptr&lt;int&gt; ptr1(new int(42));</t>
-  </si>
-  <si>
-    <t>// Hoặc dùng make_unique (C++14, an toàn hơn)</t>
-  </si>
-  <si>
-    <t>auto ptr2 = std::make_unique&lt;int&gt;(42);</t>
-  </si>
-  <si>
-    <t>// Sử dụng như raw pointer</t>
-  </si>
-  <si>
-    <t>*ptr2 = 100;</t>
-  </si>
-  <si>
-    <t>cout &lt;&lt; *ptr2;                 // 100</t>
-  </si>
-  <si>
-    <t>// Không thể copy</t>
-  </si>
-  <si>
-    <t>// auto ptr3 = ptr2;           // ERROR</t>
-  </si>
-  <si>
-    <t>// Chỉ có thể move</t>
-  </si>
-  <si>
-    <t>auto ptr3 = std::move(ptr2);   // ptr2 giờ = nullptr</t>
-  </si>
-  <si>
-    <t>if (ptr2 == nullptr) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cout &lt;&lt; "ptr2 is null";    // True</t>
-  </si>
-  <si>
-    <t>// Auto delete khi out of scope</t>
-  </si>
-  <si>
     <t>{</t>
   </si>
   <si>
-    <t xml:space="preserve">    auto ptr = std::make_unique&lt;int&gt;(10);</t>
-  </si>
-  <si>
-    <t>}   // Tự động delete, không cần delete thủ công</t>
-  </si>
-  <si>
-    <t>Với arrays:</t>
-  </si>
-  <si>
     <t>auto arr = std::make_unique&lt;int[]&gt;(100);</t>
   </si>
   <si>
-    <t>arr[0] = 42;</t>
-  </si>
-  <si>
-    <t>Khi nào dùng:</t>
-  </si>
-  <si>
-    <t>Ownership rõ ràng</t>
-  </si>
-  <si>
-    <t>Không cần share ownership</t>
-  </si>
-  <si>
-    <t>Default choice cho dynamic memory trong modern C++</t>
-  </si>
-  <si>
-    <t>Factory functions</t>
-  </si>
-  <si>
-    <t>Pimpl idiom</t>
-  </si>
-  <si>
-    <t>Managing resources</t>
-  </si>
-  <si>
-    <t>std::shared_ptr</t>
-  </si>
-  <si>
-    <t>// Tạo shared_ptr</t>
-  </si>
-  <si>
-    <t>auto ptr1 = std::make_shared&lt;int&gt;(42);</t>
-  </si>
-  <si>
-    <t>cout &lt;&lt; ptr1.use_count();      // 1</t>
-  </si>
-  <si>
-    <t>// Copy - tăng reference count</t>
-  </si>
-  <si>
-    <t>auto ptr2 = ptr1;</t>
-  </si>
-  <si>
-    <t>cout &lt;&lt; ptr1.use_count();      // 2</t>
-  </si>
-  <si>
-    <t>cout &lt;&lt; ptr2.use_count();      // 2</t>
-  </si>
-  <si>
-    <t>// ptr2 out of scope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    auto ptr3 = ptr1;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cout &lt;&lt; ptr1.use_count();  // 3</t>
-  </si>
-  <si>
-    <t>cout &lt;&lt; ptr1.use_count();      // 2 (ptr3 destroyed)</t>
-  </si>
-  <si>
-    <t>// Object deleted khi count = 0</t>
-  </si>
-  <si>
-    <t>ptr1.reset();                  // count = 1</t>
-  </si>
-  <si>
-    <t>ptr2.reset();                  // count = 0 → delete object</t>
-  </si>
-  <si>
-    <t>Custom deleter:</t>
-  </si>
-  <si>
-    <t>auto ptr = std::shared_ptr&lt;FILE&gt;(</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    fopen("file.txt", "r"),</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    [](FILE* f) { fclose(f); } // Custom deleter</t>
-  </si>
-  <si>
     <t>);</t>
   </si>
   <si>
-    <t>Nhiều owners cần share object</t>
-  </si>
-  <si>
-    <t>Object lifetime không xác định rõ</t>
-  </si>
-  <si>
-    <t>Graph structures, caches</t>
-  </si>
-  <si>
-    <t>Performance overhead (atomic reference counting)</t>
-  </si>
-  <si>
-    <t>std::weak_ptr</t>
-  </si>
-  <si>
     <t>auto shared = std::make_shared&lt;int&gt;(42);</t>
   </si>
   <si>
     <t>std::weak_ptr&lt;int&gt; weak = shared;</t>
   </si>
   <si>
-    <t>cout &lt;&lt; weak.use_count();      // 1 (không tăng count)</t>
-  </si>
-  <si>
-    <t>// Kiểm tra object còn tồn tại</t>
-  </si>
-  <si>
     <t>if (auto locked = weak.lock()) {</t>
   </si>
   <si>
@@ -1535,55 +1376,7 @@
     <t>} else {</t>
   </si>
   <si>
-    <t xml:space="preserve">    cout &lt;&lt; "Object deleted";</t>
-  </si>
-  <si>
-    <t>// Object deleted</t>
-  </si>
-  <si>
     <t>shared.reset();</t>
-  </si>
-  <si>
-    <t>if (weak.expired()) {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    cout &lt;&lt; "Weak ptr expired"; // True</t>
-  </si>
-  <si>
-    <t>Giải quyết circular reference:</t>
-  </si>
-  <si>
-    <t>struct Node {</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    std::shared_ptr&lt;Node&gt; next;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    std::weak_ptr&lt;Node&gt; prev;  // Dùng weak_ptr để break cycle</t>
-  </si>
-  <si>
-    <t>auto node1 = std::make_shared&lt;Node&gt;();</t>
-  </si>
-  <si>
-    <t>auto node2 = std::make_shared&lt;Node&gt;();</t>
-  </si>
-  <si>
-    <t>node1-&gt;next = node2;</t>
-  </si>
-  <si>
-    <t>node2-&gt;prev = node1;           // Không tạo cycle</t>
-  </si>
-  <si>
-    <t>// Cả hai sẽ tự động delete</t>
-  </si>
-  <si>
-    <t>Break circular references</t>
-  </si>
-  <si>
-    <t>Cache implementations</t>
-  </si>
-  <si>
-    <t>Observer pattern</t>
   </si>
   <si>
     <t>std::make_unique, std::make_shared</t>
@@ -2044,86 +1837,6 @@
     <t xml:space="preserve">Định nghĩa: Reference đến temporary objects (rvalue), ký hiệu &amp;&amp;. </t>
   </si>
   <si>
-    <r>
-      <t>Stack:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Tự động quản lý, nhanh, kích thước hạn chế</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Heap:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Manual quản lý, chậm hơn, kích thước lớn hơn</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Luôn set pointer = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nullptr sau delete</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Performance:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> make_shared chỉ allocate một lần (object + control block) thay vì hai lần</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>make_shared</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: memory không free cho đến khi tất cả weak_ptr cũng destroyed</t>
-    </r>
-  </si>
-  <si>
     <t>Dùng delete thay vì delete[] cho array → undefined behavior</t>
   </si>
   <si>
@@ -2133,119 +1846,21 @@
     <t>delete rồi vẫn dùng pointer → dangling pointer</t>
   </si>
   <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Cấp phát và giải phóng dynamic arrays. Phải dùng cặp new[] với delete[].</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> new cấp phát bộ nhớ động trên heap và trả về pointer. </t>
-    </r>
-  </si>
-  <si>
     <t>delete giải phóng bộ nhớ đã cấp phát.</t>
   </si>
   <si>
     <t>gây lãng phí memory và có thể crash chương trình.</t>
   </si>
   <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bộ nhớ được cấp phát nhưng không được giải phóng, </t>
-    </r>
-  </si>
-  <si>
     <t>Dereferencing dangling pointer → undefined behavior.</t>
   </si>
   <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Pointer trỏ đến vùng nhớ đã bị giải phóng. </t>
-    </r>
-  </si>
-  <si>
     <t>→ undefined behavior, thường crash chương trình.</t>
   </si>
   <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Delete cùng một pointer nhiều lần </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>tránh memory leaks và dangling pointers. Nằm trong header &lt;memory&gt;.</t>
   </si>
   <si>
-    <t>- chỉ một unique_ptr được sở hữu object tại một thời điểm. Không thể copy, chỉ có thể move.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Định nghĩa: Smart pointer với exclusive ownership </t>
-  </si>
-  <si>
-    <t>Sử dụng reference counting, object bị destroy khi count = 0.</t>
-  </si>
-  <si>
-    <t>Dùng để break circular references và observe object mà không own nó.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Định nghĩa: Smart pointer không tăng reference count của shared_ptr. </t>
-  </si>
-  <si>
     <t>Hữu ích cho non-memory resources.</t>
   </si>
   <si>
@@ -2253,86 +1868,6 @@
   </si>
   <si>
     <t>Định nghĩa: Factory functions tạo smart pointers an toàn và hiệu quả hơn việc dùng new trực tiếp.</t>
-  </si>
-  <si>
-    <r>
-      <t>Lưu ý:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Với unique_ptr, deleter là part of type. Với shared_ptr, không phải.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> RAII (Resource Acquisition Is Initialization) là design pattern trong C++ - resource được acquire trong constructor và release trong destructor. Đảm bảo cleanup tự động.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Nguyên tắc:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Constructor chịu trách nhiệm acquire tất cả resources (memory, files, locks, connections).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Nguyên tắc:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Destructor tự động giải phóng resources khi object destroyed (out of scope, exception, delete).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> RAII đảm bảo resources được cleanup ngay cả khi có exception. Stack unwinding tự động gọi destructors.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2384,22 +1919,6 @@
   </si>
   <si>
     <r>
-      <t>Định nghĩa:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="163"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Resources tự động quản lý theo scope. Khi object out of scope, resources tự động released.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>std::unique_ptr</t>
     </r>
     <r>
@@ -2466,20 +1985,1363 @@
     <t xml:space="preserve">Định nghĩa: Wrapper classes Template quản lý lifetime của pointers tự động, </t>
   </si>
   <si>
-    <t xml:space="preserve">Định nghĩa: Smart pointer với shared ownership </t>
-  </si>
-  <si>
-    <t xml:space="preserve">- nhiều shared_ptr có thể cùng sở hữu một object. </t>
-  </si>
-  <si>
-    <t>Circular references → memory leak (dùng weak_ptr để fix)</t>
+    <t>std::unique_ptr - Exclusive Ownership</t>
+  </si>
+  <si>
+    <t>Core Properties</t>
+  </si>
+  <si>
+    <t>1. Construction</t>
+  </si>
+  <si>
+    <t>// Constructor từ raw pointer</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;int&gt; p1(new int(42));</t>
+  </si>
+  <si>
+    <t>// make_unique (C++14) - PREFERRED</t>
+  </si>
+  <si>
+    <t>auto p2 = std::make_unique&lt;int&gt;(42);</t>
+  </si>
+  <si>
+    <t>// Array version</t>
+  </si>
+  <si>
+    <t>// Custom deleter</t>
+  </si>
+  <si>
+    <t>auto deleter = [](FILE* f) { if(f) fclose(f); };</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;FILE, decltype(deleter)&gt; file(fopen("data.txt", "r"), deleter);</t>
+  </si>
+  <si>
+    <t>// Default construction (nullptr)</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;int&gt; p3;  // p3 == nullptr</t>
+  </si>
+  <si>
+    <t>2. get() - Lấy raw pointer</t>
+  </si>
+  <si>
+    <t>auto ptr = std::make_unique&lt;int&gt;(42);</t>
+  </si>
+  <si>
+    <t>int* raw = ptr.get();          // Lấy raw pointer</t>
+  </si>
+  <si>
+    <t>*raw = 100;                    // OK: modify thông qua raw</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *ptr;                  // 100</t>
+  </si>
+  <si>
+    <t>// Use case: C APIs</t>
+  </si>
+  <si>
+    <t>void legacyFunc(int* p);</t>
+  </si>
+  <si>
+    <t>legacyFunc(ptr.get());         // Pass raw pointer</t>
+  </si>
+  <si>
+    <t>// Warning: ĐỪNG delete raw pointer!</t>
+  </si>
+  <si>
+    <t>// delete ptr.get();           // DISASTER! double delete</t>
+  </si>
+  <si>
+    <t>3. release() - Nhả ownership</t>
+  </si>
+  <si>
+    <t>int* raw = ptr.release();      // ptr giờ = nullptr, raw owns object</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; (ptr == nullptr);      // true</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *raw;                  // 42</t>
+  </si>
+  <si>
+    <t>// Bạn chịu trách nhiệm delete!</t>
+  </si>
+  <si>
+    <t>delete raw;</t>
+  </si>
+  <si>
+    <t>// Use case: Transfer ownership to legacy code</t>
+  </si>
+  <si>
+    <t>int* createResource() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto ptr = std::make_unique&lt;int&gt;(100);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return ptr.release();      // Caller owns pointer</t>
+  </si>
+  <si>
+    <t>4. reset() - Thay thế managed object</t>
+  </si>
+  <si>
+    <t>ptr.reset();                   // Delete object, ptr = nullptr</t>
+  </si>
+  <si>
+    <t>ptr.reset(new int(100));       // Quản lý object mới</t>
+  </si>
+  <si>
+    <t>// Use case: Reuse unique_ptr</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;Widget&gt; widget = std::make_unique&lt;Widget&gt;();</t>
+  </si>
+  <si>
+    <t>// ... use widget</t>
+  </si>
+  <si>
+    <t>widget.reset(new Widget());    // Replace với new object</t>
+  </si>
+  <si>
+    <t>5. swap() - Đổi ownership</t>
+  </si>
+  <si>
+    <t>auto p1 = std::make_unique&lt;int&gt;(10);</t>
+  </si>
+  <si>
+    <t>auto p2 = std::make_unique&lt;int&gt;(20);</t>
+  </si>
+  <si>
+    <t>p1.swap(p2);</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *p1 &lt;&lt; " " &lt;&lt; *p2;     // 20 10</t>
+  </si>
+  <si>
+    <t>// Hoặc dùng std::swap</t>
+  </si>
+  <si>
+    <t>std::swap(p1, p2);</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *p1 &lt;&lt; " " &lt;&lt; *p2;     // 10 20</t>
+  </si>
+  <si>
+    <t>6. operator bool - Kiểm tra null</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;int&gt; ptr;</t>
+  </si>
+  <si>
+    <t>if (ptr) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Not null";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Null";            // This</t>
+  </si>
+  <si>
+    <t>if (!ptr) {</t>
+  </si>
+  <si>
+    <t>struct Point {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int x, y;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void print() { cout &lt;&lt; x &lt;&lt; "," &lt;&lt; y; }</t>
+  </si>
+  <si>
+    <t>auto p = std::make_unique&lt;Point&gt;();</t>
+  </si>
+  <si>
+    <t>p-&gt;x = 10;                     // operator-&gt;</t>
+  </si>
+  <si>
+    <t>p-&gt;y = 20;</t>
+  </si>
+  <si>
+    <t>(*p).print();                  // operator* + member access</t>
+  </si>
+  <si>
+    <t>8. Comparison operators</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; (p1 == nullptr);       // false</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; (p1 != nullptr);       // true</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; (p1 &lt; p2);             // Compare addresses</t>
+  </si>
+  <si>
+    <t>9. Move semantics (NO COPY)</t>
+  </si>
+  <si>
+    <t>auto p1 = std::make_unique&lt;int&gt;(42);</t>
+  </si>
+  <si>
+    <t>// auto p2 = p1;               // ERROR: cannot copy</t>
+  </si>
+  <si>
+    <t>auto p2 = std::move(p1);       // OK: move ownership</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; (p1 == nullptr);       // true</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *p2;                   // 42</t>
+  </si>
+  <si>
+    <t>// Return from function (automatic move)</t>
+  </si>
+  <si>
+    <t>std::unique_ptr&lt;int&gt; create() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return ptr;                // Implicit move</t>
+  </si>
+  <si>
+    <t>auto p = create();             // No copy, just move</t>
+  </si>
+  <si>
+    <t>std::shared_ptr - Shared Ownership</t>
+  </si>
+  <si>
+    <t>// make_shared (PREFERRED - hiệu quả nhất)</t>
+  </si>
+  <si>
+    <t>auto p1 = std::make_shared&lt;int&gt;(42);</t>
+  </si>
+  <si>
+    <t>std::shared_ptr&lt;int&gt; p2(new int(42));</t>
+  </si>
+  <si>
+    <t>// Copy constructor (tăng ref count)</t>
+  </si>
+  <si>
+    <t>auto p3 = p1;                  // ref count = 2</t>
+  </si>
+  <si>
+    <t>// Constructor từ unique_ptr (transfer ownership)</t>
+  </si>
+  <si>
+    <t>auto uptr = std::make_unique&lt;int&gt;(100);</t>
+  </si>
+  <si>
+    <t>std::shared_ptr&lt;int&gt; sptr = std::move(uptr);  // uptr = nullptr</t>
+  </si>
+  <si>
+    <t>// Array (C++17)</t>
+  </si>
+  <si>
+    <t>std::shared_ptr&lt;int[]&gt; arr(new int[10]);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Deleting\n"; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    delete p; </t>
+  </si>
+  <si>
+    <t>std::shared_ptr&lt;int&gt; p4(new int(42), deleter);</t>
+  </si>
+  <si>
+    <t>2. use_count() - Reference count</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p1.use_count();        // 1</t>
+  </si>
+  <si>
+    <t>auto p2 = p1;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p1.use_count();        // 2</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p2.use_count();        // 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto p3 = p1;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; p1.use_count();    // 3</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p1.use_count();        // 2 (p3 destroyed)</t>
+  </si>
+  <si>
+    <t>p2.reset();</t>
+  </si>
+  <si>
+    <t>3. unique() - Kiểm tra sole owner</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p1.unique();           // true (count = 1)</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p1.unique();           // false (count = 2)</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p2.unique();           // false</t>
+  </si>
+  <si>
+    <t>4. get() - Raw pointer</t>
+  </si>
+  <si>
+    <t>auto ptr = std::make_shared&lt;int&gt;(42);</t>
+  </si>
+  <si>
+    <t>int* raw = ptr.get();</t>
+  </si>
+  <si>
+    <t>// Use with C APIs</t>
+  </si>
+  <si>
+    <t>void cFunc(int* p);</t>
+  </si>
+  <si>
+    <t>cFunc(ptr.get());</t>
+  </si>
+  <si>
+    <t>// ĐỪNG delete raw pointer!</t>
+  </si>
+  <si>
+    <t>// delete ptr.get();           // DISASTER!</t>
+  </si>
+  <si>
+    <t>5. reset() - Giảm ref count hoặc reassign</t>
+  </si>
+  <si>
+    <t>auto p2 = p1;                  // count = 2</t>
+  </si>
+  <si>
+    <t>p1.reset();                    // p1 = nullptr, count = 1</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; p2.use_count();        // 1</t>
+  </si>
+  <si>
+    <t>p2.reset(new int(100));        // p2 owns new object, old deleted</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *p2;                   // 100</t>
+  </si>
+  <si>
+    <t>6. operator=, copy/move assignment</t>
+  </si>
+  <si>
+    <t>auto p1 = std::make_shared&lt;int&gt;(10);</t>
+  </si>
+  <si>
+    <t>auto p2 = std::make_shared&lt;int&gt;(20);</t>
+  </si>
+  <si>
+    <t>// Copy assignment (tăng ref count của p1, giảm của p2)</t>
+  </si>
+  <si>
+    <t>p2 = p1;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *p2;                   // 10</t>
+  </si>
+  <si>
+    <t>// Move assignment</t>
+  </si>
+  <si>
+    <t>auto p3 = std::make_shared&lt;int&gt;(30);</t>
+  </si>
+  <si>
+    <t>p3 = std::move(p1);            // p1 = nullptr, p3 owns p1's object</t>
+  </si>
+  <si>
+    <t>7. swap() - Đổi ownership</t>
+  </si>
+  <si>
+    <t>8. owner_before() - Ordering trong containers</t>
+  </si>
+  <si>
+    <t>std::map&lt;std::shared_ptr&lt;int&gt;, string, std::owner_less&lt;&gt;&gt; myMap;</t>
+  </si>
+  <si>
+    <t>myMap[p1] = "value";</t>
+  </si>
+  <si>
+    <t>// owner_before ensures consistent ordering</t>
+  </si>
+  <si>
+    <t>9. Aliasing constructor</t>
+  </si>
+  <si>
+    <t>struct Data {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int value;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    string name;</t>
+  </si>
+  <si>
+    <t>auto dataPtr = std::make_shared&lt;Data&gt;();</t>
+  </si>
+  <si>
+    <t>dataPtr-&gt;value = 42;</t>
+  </si>
+  <si>
+    <t>dataPtr-&gt;name = "test";</t>
+  </si>
+  <si>
+    <t>// Aliasing: share ownership với dataPtr, nhưng point to member</t>
+  </si>
+  <si>
+    <t>std::shared_ptr&lt;int&gt; valuePtr(dataPtr, &amp;dataPtr-&gt;value);</t>
+  </si>
+  <si>
+    <t>std::shared_ptr&lt;string&gt; namePtr(dataPtr, &amp;dataPtr-&gt;name);</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; valuePtr.use_count();  // 3 (dataPtr, valuePtr, namePtr)</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; *valuePtr;             // 42</t>
+  </si>
+  <si>
+    <t>// dataPtr destroyed khi cả 3 pointers destroyed</t>
+  </si>
+  <si>
+    <t>std::weak_ptr - Non-owning Observer</t>
+  </si>
+  <si>
+    <t>// Từ shared_ptr</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; weak1(shared);</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; weak2 = shared;</t>
+  </si>
+  <si>
+    <t>// Copy từ weak_ptr khác</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; weak3 = weak1;</t>
+  </si>
+  <si>
+    <t>// KHÔNG thể construct từ raw pointer</t>
+  </si>
+  <si>
+    <t>// std::weak_ptr&lt;int&gt; weak(new int(42));  // ERROR</t>
+  </si>
+  <si>
+    <t>2. expired() - Kiểm tra object còn tồn tại</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; weak.expired();        // false</t>
+  </si>
+  <si>
+    <t>shared.reset();                // Delete object</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; weak.expired();        // true</t>
+  </si>
+  <si>
+    <t>3. lock() - Lấy shared_ptr</t>
+  </si>
+  <si>
+    <t>// Lock để access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; locked.use_count();  // 2 (shared + locked)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Object destroyed";</t>
+  </si>
+  <si>
+    <t>// Sau khi out of scope, locked destroyed</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; shared.use_count();    // 1</t>
+  </si>
+  <si>
+    <t>// Object destroyed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Không vào đây</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; "Object destroyed";  // This</t>
+  </si>
+  <si>
+    <t>Thread-safe pattern:</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;Resource&gt; weak;</t>
+  </si>
+  <si>
+    <t>void accessResource() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto locked = weak.lock();  // Atomic check + acquire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (locked) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        locked-&gt;use();          // Safe: object won't be deleted</t>
+  </si>
+  <si>
+    <t>4. use_count() - Observer ref count</t>
+  </si>
+  <si>
+    <t>auto s1 = std::make_shared&lt;int&gt;(42);</t>
+  </si>
+  <si>
+    <t>auto s2 = s1;</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; w = s1;</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; w.use_count();         // 2 (s1, s2)</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; s1.use_count();        // 2</t>
+  </si>
+  <si>
+    <t>s2.reset();</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; w.use_count();         // 1</t>
+  </si>
+  <si>
+    <t>5. reset() - Clear weak_ptr</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; weak;</t>
+  </si>
+  <si>
+    <t>weak = shared;</t>
+  </si>
+  <si>
+    <t>weak.reset();                  // Clear weak_ptr</t>
+  </si>
+  <si>
+    <t>cout &lt;&lt; weak.expired();        // true (nhưng object vẫn còn)</t>
+  </si>
+  <si>
+    <t>6. swap() - Đổi weak_ptr</t>
+  </si>
+  <si>
+    <t>auto s1 = std::make_shared&lt;int&gt;(10);</t>
+  </si>
+  <si>
+    <t>auto s2 = std::make_shared&lt;int&gt;(20);</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; w1 = s1;</t>
+  </si>
+  <si>
+    <t>std::weak_ptr&lt;int&gt; w2 = s2;</t>
+  </si>
+  <si>
+    <t>w1.swap(w2);</t>
+  </si>
+  <si>
+    <t>if (auto locked = w1.lock()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; *locked;           // 20</t>
+  </si>
+  <si>
+    <t>7. operator= - Assignment</t>
+  </si>
+  <si>
+    <t>weak = s1;                     // Observe s1</t>
+  </si>
+  <si>
+    <t>if (auto l = weak.lock()) cout &lt;&lt; *l;  // 10</t>
+  </si>
+  <si>
+    <t>weak = s2;                     // Now observe s2</t>
+  </si>
+  <si>
+    <t>if (auto l = weak.lock()) cout &lt;&lt; *l;  // 20</t>
+  </si>
+  <si>
+    <t>Solving Circular Reference Problem</t>
+  </si>
+  <si>
+    <t>Problem: Memory leak với circular references</t>
+  </si>
+  <si>
+    <t>// BAD: Circular reference → memory leak</t>
+  </si>
+  <si>
+    <t>struct Node {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::shared_ptr&lt;Node&gt; next;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::shared_ptr&lt;Node&gt; prev;  // Circular!</t>
+  </si>
+  <si>
+    <t>auto n1 = std::make_shared&lt;Node&gt;();</t>
+  </si>
+  <si>
+    <t>auto n2 = std::make_shared&lt;Node&gt;();</t>
+  </si>
+  <si>
+    <t>n1-&gt;next = n2;                 // n2 count = 2</t>
+  </si>
+  <si>
+    <t>n2-&gt;prev = n1;                 // n1 count = 2</t>
+  </si>
+  <si>
+    <t>// Khi n1, n2 out of scope:</t>
+  </si>
+  <si>
+    <t>// n1 count = 1 (vì n2-&gt;prev still points)</t>
+  </si>
+  <si>
+    <t>// n2 count = 1 (vì n1-&gt;next still points)</t>
+  </si>
+  <si>
+    <t>// → MEMORY LEAK! Cả hai không bao giờ deleted</t>
+  </si>
+  <si>
+    <t>Solution: Dùng weak_ptr để break cycle</t>
+  </si>
+  <si>
+    <t>// GOOD: Break circular reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::weak_ptr&lt;Node&gt; prev;    // weak_ptr! Không tăng count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    ~Node() { cout &lt;&lt; "Node destroyed\n"; }</t>
+  </si>
+  <si>
+    <t>n2-&gt;prev = n1;                 // n1 count = 1 (weak không tăng)</t>
+  </si>
+  <si>
+    <t>// n1 count = 0 → deleted</t>
+  </si>
+  <si>
+    <t>// n2 count = 1 → 0 → deleted</t>
+  </si>
+  <si>
+    <t>// ✓ No memory leak!</t>
+  </si>
+  <si>
+    <t>// Access prev safely</t>
+  </si>
+  <si>
+    <t>if (auto prevNode = n2-&gt;prev.lock()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; prevNode-&gt;value;</t>
+  </si>
+  <si>
+    <t>Observer Pattern Example</t>
+  </si>
+  <si>
+    <t>class Subject {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    vector&lt;std::weak_ptr&lt;Observer&gt;&gt; observers;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void attach(std::shared_ptr&lt;Observer&gt; obs) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        observers.push_back(obs);  // weak_ptr: không prevent deletion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    void notify() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Remove expired observers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        observers.erase(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            std::remove_if(observers.begin(), observers.end(),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                [](const auto&amp; weak) { return weak.expired(); }),</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            observers.end()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        );</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Notify active observers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        for (auto&amp; weak : observers) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (auto obs = weak.lock()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                obs-&gt;update();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            }</t>
+  </si>
+  <si>
+    <t>class Observer {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual void update() = 0;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    virtual ~Observer() { cout &lt;&lt; "Observer destroyed\n"; }</t>
+  </si>
+  <si>
+    <t>// Usage</t>
+  </si>
+  <si>
+    <t>Subject subject;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto obs1 = std::make_shared&lt;ConcreteObserver&gt;();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto obs2 = std::make_shared&lt;ConcreteObserver&gt;();</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    subject.attach(obs1);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    subject.attach(obs2);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    subject.notify();          // Both notified</t>
+  </si>
+  <si>
+    <t>// obs1, obs2 destroyed (out of scope)</t>
+  </si>
+  <si>
+    <t>subject.notify();              // No observers (automatically cleaned)</t>
+  </si>
+  <si>
+    <t>Cache Implementation Example</t>
+  </si>
+  <si>
+    <t>class ResourceCache {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::map&lt;string, std::weak_ptr&lt;Resource&gt;&gt; cache;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    std::shared_ptr&lt;Resource&gt; get(const string&amp; key) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        auto it = cache.find(key);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        if (it != cache.end()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            // Try to get cached resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            if (auto resource = it-&gt;second.lock()) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                cout &lt;&lt; "Cache hit\n";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                return resource;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">            } else {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                // Resource destroyed, remove from cache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                cache.erase(it);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Load resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cout &lt;&lt; "Cache miss, loading...\n";</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        auto resource = std::make_shared&lt;Resource&gt;(key);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        cache[key] = resource;     // Store weak_ptr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        return resource;</t>
+  </si>
+  <si>
+    <t>ResourceCache cache;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto res1 = cache.get("texture1");  // Load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    auto res2 = cache.get("texture1");  // Cache hit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    cout &lt;&lt; res1.use_count();  // 2 (res1, res2)</t>
+  </si>
+  <si>
+    <t>// Resources destroyed (out of scope)</t>
+  </si>
+  <si>
+    <t>auto res3 = cache.get("texture1");  // Cache miss (reload)</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> new cấp phát bộ nhớ động trên heap và trả về pointer. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Cấp phát và giải phóng dynamic arrays. Phải dùng cặp new[] với delete[].</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Stack:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tự động quản lý, nhanh, kích thước hạn chế</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Heap:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Manual quản lý, chậm hơn, kích thước lớn hơn</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bộ nhớ được cấp phát nhưng không được giải phóng, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Pointer trỏ đến vùng nhớ đã bị giải phóng. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Delete cùng một pointer nhiều lần </t>
+    </r>
+  </si>
+  <si>
+    <t>Luôn set pointer = nullptr sau delete</t>
+  </si>
+  <si>
+    <r>
+      <t>Performance:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> make_shared chỉ allocate một lần (object + control block) thay vì hai lần</t>
+    </r>
+  </si>
+  <si>
+    <t>make_shared: memory không free cho đến khi tất cả weak_ptr cũng destroyed</t>
+  </si>
+  <si>
+    <r>
+      <t>Lưu ý:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Với unique_ptr, deleter là part of type. Với shared_ptr, không phải.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use case:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Access members mà vẫn keep object alive.</t>
+    </r>
+  </si>
+  <si>
+    <t>Không thể copy, chỉ move. Nhẹ nhất trong các smart pointers.</t>
+  </si>
+  <si>
+    <t>Dùng khi cần pass to legacy APIs.</t>
+  </si>
+  <si>
+    <t>Transfer ownership ra ngoài.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple shared_ptr có thể own cùng object. </t>
+  </si>
+  <si>
+    <t>Object deleted khi reference count = 0.</t>
+  </si>
+  <si>
+    <t>Không nên dùng để check ownership logic.</t>
+  </si>
+  <si>
+    <t>Không tăng reference count. Dùng để break circular references và observe mà không own.</t>
+  </si>
+  <si>
+    <t>Trả về shared_ptr nếu object còn, nullptr nếu expired.</t>
+  </si>
+  <si>
+    <t>chỉ count strong references (shared_ptr).</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Exclusive ownership - chỉ một unique_ptr sở hữu object. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Shared ownership với reference counting. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Non-owning reference đến object được quản lý bởi shared_ptr. </t>
+    </r>
+  </si>
+  <si>
+    <t>- resource được acquire trong constructor và release trong destructor. Đảm bảo cleanup tự động.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> RAII (Resource Acquisition Is Initialization) là design pattern trong C++ </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Nguyên tắc:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Destructor tự động giải phóng resources </t>
+    </r>
+  </si>
+  <si>
+    <t>khi object destroyed (out of scope, exception, delete).</t>
+  </si>
+  <si>
+    <r>
+      <t>Nguyên tắc:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Constructor chịu trách nhiệm acquire </t>
+    </r>
+  </si>
+  <si>
+    <t>tất cả resources (memory, files, locks, connections).</t>
+  </si>
+  <si>
+    <t>Stack unwinding tự động gọi destructors.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> RAII đảm bảo resources được cleanup ngay cả khi có exception. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Resources tự động quản lý theo scope. </t>
+    </r>
+  </si>
+  <si>
+    <t>Khi object out of scope, resources tự động released.</t>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Trả về raw pointer mà không transfer ownership. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Trả về raw pointer và set unique_ptr = nullptr. </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Delete object hiện tại và optionally quản lý object mới.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7. operator, operator-&gt; - Dereferencing</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Trả về số lượng shared_ptr đang own object.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lưu ý:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> use_count() có thể chậm với multithreading (atomic operations). </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Note:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> unique() deprecated trong C++17, dùng use_count() == 1 thay thế.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> So sánh ownership order, dùng trong std::map, std::set với shared_ptr.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Định nghĩa:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Chia sẻ ownership với object khác nhưng trỏ đến member.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Định nghĩa: Attempt to get shared_ptr từ weak_ptr. </t>
+  </si>
+  <si>
+    <r>
+      <t>Lưu ý:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> use_count() không count weak references, </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Định nghĩa: Trả về </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nếu object đã </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bị destroyed</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ref count = 0).</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2500,14 +3362,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2546,7 +3400,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
@@ -2554,7 +3437,8 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="163"/>
@@ -2644,7 +3528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2660,8 +3544,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2671,53 +3555,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3055,17 +3978,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AM20"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="6" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" s="6" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3076,7 +3999,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -3087,7 +4010,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
@@ -3098,7 +4021,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
@@ -3109,7 +4032,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
@@ -3120,7 +4043,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>20</v>
       </c>
@@ -3131,19 +4054,19 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>3</v>
       </c>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="1:39" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="S9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>21</v>
       </c>
@@ -3151,7 +4074,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>22</v>
       </c>
@@ -3159,7 +4082,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
@@ -3167,7 +4090,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>23</v>
       </c>
@@ -3175,7 +4098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>24</v>
       </c>
@@ -3183,30 +4106,30 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
     </row>
-    <row r="16" spans="1:39" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>7</v>
       </c>
@@ -3219,17 +4142,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BL96"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" s="14" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>37</v>
       </c>
@@ -3277,7 +4200,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AG5" s="11" t="s">
         <v>39</v>
       </c>
@@ -3285,7 +4208,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>39</v>
       </c>
@@ -3296,7 +4219,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>40</v>
       </c>
@@ -3307,7 +4230,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>41</v>
       </c>
@@ -3318,7 +4241,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>42</v>
       </c>
@@ -3338,7 +4261,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AG10" s="15" t="s">
         <v>52</v>
       </c>
@@ -3361,7 +4284,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>44</v>
       </c>
@@ -3373,7 +4296,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>193</v>
       </c>
@@ -3385,12 +4308,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AG14" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:62" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>182</v>
       </c>
@@ -3438,7 +4361,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>45</v>
       </c>
@@ -3446,7 +4369,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>46</v>
       </c>
@@ -3454,7 +4377,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="21" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>47</v>
       </c>
@@ -3462,7 +4385,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE22" s="11"/>
     </row>
     <row r="23" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3473,7 +4396,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="22" t="s">
         <v>191</v>
       </c>
@@ -3481,7 +4404,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>192</v>
       </c>
@@ -3491,45 +4414,45 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE27" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE28" s="10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE30" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE31" s="11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="32" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE32" s="11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE33" s="11"/>
     </row>
-    <row r="34" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE34" s="11" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BE35" s="11" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>77</v>
       </c>
@@ -3570,7 +4493,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="39" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="20" t="s">
         <v>201</v>
       </c>
@@ -3581,7 +4504,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="40" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
         <v>78</v>
       </c>
@@ -3592,7 +4515,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="AC41" s="8" t="s">
         <v>179</v>
@@ -3601,7 +4524,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>203</v>
       </c>
@@ -3609,7 +4532,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>79</v>
       </c>
@@ -3618,7 +4541,7 @@
       </c>
       <c r="BB43" s="11"/>
     </row>
-    <row r="44" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AC44" s="11"/>
       <c r="BB44" s="11" t="s">
         <v>105</v>
@@ -3635,7 +4558,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="46" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>80</v>
       </c>
@@ -3646,7 +4569,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="47" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>81</v>
       </c>
@@ -3655,7 +4578,7 @@
       </c>
       <c r="BB47" s="11"/>
     </row>
-    <row r="48" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:58" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>82</v>
       </c>
@@ -3666,13 +4589,13 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AC49" s="11"/>
       <c r="BB49" s="11" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="11" t="s">
         <v>83</v>
       </c>
@@ -3683,7 +4606,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="51" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>84</v>
       </c>
@@ -3702,7 +4625,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="53" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>86</v>
       </c>
@@ -3713,7 +4636,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>56</v>
       </c>
@@ -3738,7 +4661,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="57" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AC57" s="11" t="s">
         <v>100</v>
       </c>
@@ -3746,7 +4669,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AC58" s="11" t="s">
         <v>101</v>
       </c>
@@ -3754,7 +4677,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="59" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BB59" s="10" t="s">
         <v>185</v>
       </c>
@@ -3767,7 +4690,7 @@
     <row r="61" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AC61" s="7"/>
     </row>
-    <row r="62" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="15" t="s">
         <v>114</v>
       </c>
@@ -3803,7 +4726,7 @@
         <v>212</v>
       </c>
       <c r="BD63" s="18" t="s">
-        <v>512</v>
+        <v>443</v>
       </c>
     </row>
     <row r="64" spans="1:64" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3814,7 +4737,7 @@
         <v>211</v>
       </c>
       <c r="BD64" s="18" t="s">
-        <v>509</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3837,7 +4760,7 @@
       </c>
       <c r="BE66" s="20"/>
     </row>
-    <row r="67" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>39</v>
       </c>
@@ -3849,7 +4772,7 @@
       </c>
       <c r="BE67" s="20"/>
     </row>
-    <row r="68" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>116</v>
       </c>
@@ -3859,7 +4782,7 @@
       </c>
       <c r="BE68" s="20"/>
     </row>
-    <row r="69" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>117</v>
       </c>
@@ -3871,7 +4794,7 @@
       </c>
       <c r="BE69" s="20"/>
     </row>
-    <row r="70" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>118</v>
       </c>
@@ -3883,7 +4806,7 @@
       </c>
       <c r="BE70" s="20"/>
     </row>
-    <row r="71" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="BD71" s="19"/>
       <c r="BE71" s="20"/>
@@ -3900,7 +4823,7 @@
       </c>
       <c r="BE72" s="20"/>
     </row>
-    <row r="73" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AK73" s="10" t="s">
         <v>153</v>
       </c>
@@ -3909,19 +4832,19 @@
       </c>
       <c r="BE73" s="20"/>
     </row>
-    <row r="74" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="25" t="s">
+    <row r="74" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
-      <c r="D74" s="26"/>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26"/>
-      <c r="G74" s="26"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="24"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="24"/>
       <c r="AK74" s="10" t="s">
         <v>154</v>
       </c>
@@ -3939,152 +4862,152 @@
       </c>
     </row>
     <row r="76" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="23" t="s">
+      <c r="B76" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="C76" s="23"/>
-      <c r="D76" s="23"/>
-      <c r="E76" s="23"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="23" t="s">
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="H76" s="23"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="23"/>
-      <c r="K76" s="23"/>
-      <c r="L76" s="23"/>
-      <c r="M76" s="23"/>
-      <c r="N76" s="23"/>
-      <c r="O76" s="23" t="s">
+      <c r="H76" s="45"/>
+      <c r="I76" s="45"/>
+      <c r="J76" s="45"/>
+      <c r="K76" s="45"/>
+      <c r="L76" s="45"/>
+      <c r="M76" s="45"/>
+      <c r="N76" s="45"/>
+      <c r="O76" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="P76" s="23"/>
-      <c r="Q76" s="23"/>
-      <c r="R76" s="23"/>
-      <c r="S76" s="23"/>
+      <c r="P76" s="45"/>
+      <c r="Q76" s="45"/>
+      <c r="R76" s="45"/>
+      <c r="S76" s="45"/>
       <c r="BD76" s="7" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="77" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B77" s="24" t="s">
+    <row r="77" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="24"/>
-      <c r="F77" s="24"/>
-      <c r="G77" s="24" t="s">
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
-      <c r="J77" s="24"/>
-      <c r="K77" s="24"/>
-      <c r="L77" s="24"/>
-      <c r="M77" s="24"/>
-      <c r="N77" s="24"/>
-      <c r="O77" s="24" t="s">
+      <c r="H77" s="44"/>
+      <c r="I77" s="44"/>
+      <c r="J77" s="44"/>
+      <c r="K77" s="44"/>
+      <c r="L77" s="44"/>
+      <c r="M77" s="44"/>
+      <c r="N77" s="44"/>
+      <c r="O77" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="P77" s="24"/>
-      <c r="Q77" s="24"/>
-      <c r="R77" s="24"/>
-      <c r="S77" s="24"/>
+      <c r="P77" s="44"/>
+      <c r="Q77" s="44"/>
+      <c r="R77" s="44"/>
+      <c r="S77" s="44"/>
       <c r="AK77" s="11" t="s">
         <v>156</v>
       </c>
       <c r="BD77" s="22" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="78" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B78" s="24" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="78" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="C78" s="24"/>
-      <c r="D78" s="24"/>
-      <c r="E78" s="24"/>
-      <c r="F78" s="24"/>
-      <c r="G78" s="24" t="s">
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="H78" s="24"/>
-      <c r="I78" s="24"/>
-      <c r="J78" s="24"/>
-      <c r="K78" s="24"/>
-      <c r="L78" s="24"/>
-      <c r="M78" s="24"/>
-      <c r="N78" s="24"/>
-      <c r="O78" s="24" t="s">
+      <c r="H78" s="44"/>
+      <c r="I78" s="44"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="44"/>
+      <c r="L78" s="44"/>
+      <c r="M78" s="44"/>
+      <c r="N78" s="44"/>
+      <c r="O78" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="P78" s="24"/>
-      <c r="Q78" s="24"/>
-      <c r="R78" s="24"/>
-      <c r="S78" s="24"/>
+      <c r="P78" s="44"/>
+      <c r="Q78" s="44"/>
+      <c r="R78" s="44"/>
+      <c r="S78" s="44"/>
       <c r="AK78" s="11" t="s">
         <v>157</v>
       </c>
       <c r="BD78" s="22" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="79" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B79" s="24" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="79" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B79" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="C79" s="24"/>
-      <c r="D79" s="24"/>
-      <c r="E79" s="24"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="24" t="s">
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="H79" s="24"/>
-      <c r="I79" s="24"/>
-      <c r="J79" s="24"/>
-      <c r="K79" s="24"/>
-      <c r="L79" s="24"/>
-      <c r="M79" s="24"/>
-      <c r="N79" s="24"/>
-      <c r="O79" s="24" t="s">
+      <c r="H79" s="44"/>
+      <c r="I79" s="44"/>
+      <c r="J79" s="44"/>
+      <c r="K79" s="44"/>
+      <c r="L79" s="44"/>
+      <c r="M79" s="44"/>
+      <c r="N79" s="44"/>
+      <c r="O79" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="P79" s="24"/>
-      <c r="Q79" s="24"/>
-      <c r="R79" s="24"/>
-      <c r="S79" s="24"/>
+      <c r="P79" s="44"/>
+      <c r="Q79" s="44"/>
+      <c r="R79" s="44"/>
+      <c r="S79" s="44"/>
       <c r="AK79" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B80" s="24" t="s">
+    <row r="80" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24" t="s">
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="44"/>
+      <c r="F80" s="44"/>
+      <c r="G80" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24" t="s">
+      <c r="H80" s="44"/>
+      <c r="I80" s="44"/>
+      <c r="J80" s="44"/>
+      <c r="K80" s="44"/>
+      <c r="L80" s="44"/>
+      <c r="M80" s="44"/>
+      <c r="N80" s="44"/>
+      <c r="O80" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="P80" s="24"/>
-      <c r="Q80" s="24"/>
-      <c r="R80" s="24"/>
-      <c r="S80" s="24"/>
+      <c r="P80" s="44"/>
+      <c r="Q80" s="44"/>
+      <c r="R80" s="44"/>
+      <c r="S80" s="44"/>
       <c r="AK80" s="11" t="s">
         <v>56</v>
       </c>
@@ -4092,70 +5015,70 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="24" t="s">
+    <row r="81" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B81" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="24"/>
-      <c r="F81" s="24"/>
-      <c r="G81" s="24" t="s">
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="H81" s="24"/>
-      <c r="I81" s="24"/>
-      <c r="J81" s="24"/>
-      <c r="K81" s="24"/>
-      <c r="L81" s="24"/>
-      <c r="M81" s="24"/>
-      <c r="N81" s="24"/>
-      <c r="O81" s="24" t="s">
+      <c r="H81" s="44"/>
+      <c r="I81" s="44"/>
+      <c r="J81" s="44"/>
+      <c r="K81" s="44"/>
+      <c r="L81" s="44"/>
+      <c r="M81" s="44"/>
+      <c r="N81" s="44"/>
+      <c r="O81" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="P81" s="24"/>
-      <c r="Q81" s="24"/>
-      <c r="R81" s="24"/>
-      <c r="S81" s="24"/>
+      <c r="P81" s="44"/>
+      <c r="Q81" s="44"/>
+      <c r="R81" s="44"/>
+      <c r="S81" s="44"/>
       <c r="BD81" s="11" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="82" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B82" s="24" t="s">
+    <row r="82" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="C82" s="24"/>
-      <c r="D82" s="24"/>
-      <c r="E82" s="24"/>
-      <c r="F82" s="24"/>
-      <c r="G82" s="24" t="s">
+      <c r="C82" s="44"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="44"/>
+      <c r="G82" s="44" t="s">
         <v>139</v>
       </c>
-      <c r="H82" s="24"/>
-      <c r="I82" s="24"/>
-      <c r="J82" s="24"/>
-      <c r="K82" s="24"/>
-      <c r="L82" s="24"/>
-      <c r="M82" s="24"/>
-      <c r="N82" s="24"/>
-      <c r="O82" s="24" t="s">
+      <c r="H82" s="44"/>
+      <c r="I82" s="44"/>
+      <c r="J82" s="44"/>
+      <c r="K82" s="44"/>
+      <c r="L82" s="44"/>
+      <c r="M82" s="44"/>
+      <c r="N82" s="44"/>
+      <c r="O82" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="P82" s="24"/>
-      <c r="Q82" s="24"/>
-      <c r="R82" s="24"/>
-      <c r="S82" s="24"/>
+      <c r="P82" s="44"/>
+      <c r="Q82" s="44"/>
+      <c r="R82" s="44"/>
+      <c r="S82" s="44"/>
       <c r="BD82" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="83" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BD83" s="11" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="84" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="11" t="s">
         <v>89</v>
       </c>
@@ -4163,13 +5086,13 @@
         <v>172</v>
       </c>
     </row>
-    <row r="85" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="11"/>
       <c r="BD85" s="11" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="86" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="11" t="s">
         <v>141</v>
       </c>
@@ -4177,7 +5100,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="87" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="11" t="s">
         <v>142</v>
       </c>
@@ -4185,7 +5108,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="88" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11" t="s">
         <v>143</v>
       </c>
@@ -4193,7 +5116,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="11"/>
     </row>
     <row r="90" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4204,7 +5127,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="11" t="s">
         <v>45</v>
       </c>
@@ -4212,7 +5135,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="92" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="11" t="s">
         <v>145</v>
       </c>
@@ -4225,12 +5148,12 @@
         <v>146</v>
       </c>
     </row>
-    <row r="95" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="96" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:56" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>181</v>
       </c>
@@ -4266,2025 +5189,3479 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BG169"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:CM300"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="3" style="9"/>
+    <col min="1" max="16384" width="3" style="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="14" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:30" s="27" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="V2" s="15" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="V2" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
-      <c r="Z2" s="16"/>
-      <c r="AA2" s="16"/>
-      <c r="AB2" s="16"/>
-      <c r="AC2" s="16"/>
-      <c r="AD2" s="16"/>
-    </row>
-    <row r="3" spans="1:30" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
+        <v>738</v>
+      </c>
+      <c r="V3" s="31" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="V4" s="33" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="V5" s="33" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A6" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="V6" s="33" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A7" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="V7" s="33"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A8" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="V8" s="33" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A9" s="33"/>
+      <c r="V9" s="33" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="V10" s="33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A11" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="V11" s="33"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="V12" s="33" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="V13" s="33" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="V14" s="33" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="V15" s="33" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A16" s="35" t="s">
+        <v>740</v>
+      </c>
+      <c r="V16" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A17" s="35" t="s">
+        <v>741</v>
+      </c>
+      <c r="V17" s="33" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="18" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="V18" s="33" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="19" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="V19" s="33" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="V20" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="V21" s="33" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="23" spans="1:59" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:59" s="27" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="26" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="U25" s="28" t="s">
+        <v>253</v>
+      </c>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+      <c r="AK25" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="AL25" s="29"/>
+      <c r="AM25" s="29"/>
+      <c r="AN25" s="29"/>
+      <c r="AO25" s="29"/>
+      <c r="AP25" s="29"/>
+      <c r="AQ25" s="29"/>
+      <c r="AR25" s="29"/>
+      <c r="AZ25" s="28" t="s">
+        <v>275</v>
+      </c>
+      <c r="BA25" s="29"/>
+      <c r="BB25" s="29"/>
+      <c r="BC25" s="29"/>
+      <c r="BD25" s="29"/>
+      <c r="BE25" s="29"/>
+      <c r="BF25" s="29"/>
+      <c r="BG25" s="29"/>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
+        <v>742</v>
+      </c>
+      <c r="U26" s="31" t="s">
+        <v>743</v>
+      </c>
+      <c r="AK26" s="38" t="s">
+        <v>264</v>
+      </c>
+      <c r="AZ26" s="31" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="27" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A27" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="U27" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="AK27" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="AZ27" s="32" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="28" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="U28" s="33" t="s">
+        <v>254</v>
+      </c>
+      <c r="AK28" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ28" s="33" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A29" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="U29" s="33" t="s">
+        <v>255</v>
+      </c>
+      <c r="AK29" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="AZ29" s="33" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="U30" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="AK30" s="33"/>
+      <c r="AZ30" s="33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A31" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="U31" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="AK31" s="38" t="s">
+        <v>268</v>
+      </c>
+      <c r="AZ31" s="33" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="32" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A32" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="U32" s="33" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK32" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="AZ32" s="33"/>
+    </row>
+    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A33" s="33"/>
+      <c r="U33" s="33"/>
+      <c r="AK33" s="33" t="s">
+        <v>270</v>
+      </c>
+      <c r="AZ33" s="33" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A34" s="33" t="s">
+        <v>244</v>
+      </c>
+      <c r="U34" s="33" t="s">
+        <v>259</v>
+      </c>
+      <c r="AK34" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="AZ34" s="33" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A35" s="33" t="s">
+        <v>245</v>
+      </c>
+      <c r="U35" s="33" t="s">
+        <v>256</v>
+      </c>
+      <c r="AK35" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AZ35" s="33" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="U36" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="AK36" s="33"/>
+      <c r="AZ36" s="33" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A37" s="33" t="s">
+        <v>246</v>
+      </c>
+      <c r="U37" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="AK37" s="38" t="s">
+        <v>272</v>
+      </c>
+      <c r="AZ37" s="33"/>
+    </row>
+    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A38" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="U38" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK38" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="AZ38" s="33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A39" s="33"/>
+      <c r="U39" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK39" s="33" t="s">
+        <v>273</v>
+      </c>
+      <c r="AZ39" s="33" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A40" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="AK40" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="AZ40" s="33" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A41" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="AK41" s="33" t="s">
+        <v>274</v>
+      </c>
+      <c r="AZ41" s="33" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A42" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="AZ42" s="33" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A43" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AZ43" s="33"/>
+    </row>
+    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AZ44" s="33" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A45" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="AZ45" s="33" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A46" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="AZ46" s="33" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A47" s="36" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AZ48" s="34" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="49" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AZ49" s="39" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="50" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AZ50" s="39" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="51" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AZ51" s="39" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="52" spans="1:56" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="1:56" s="27" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="26" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="54" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A54" s="31" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="55" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A55" s="31" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="57" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
+        <v>463</v>
+      </c>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="29"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="29"/>
+      <c r="V57" s="28" t="s">
+        <v>538</v>
+      </c>
+      <c r="W57" s="29"/>
+      <c r="X57" s="29"/>
+      <c r="Y57" s="29"/>
+      <c r="Z57" s="29"/>
+      <c r="AA57" s="29"/>
+      <c r="AB57" s="29"/>
+      <c r="AC57" s="29"/>
+      <c r="AD57" s="29"/>
+      <c r="AE57" s="29"/>
+      <c r="AF57" s="29"/>
+      <c r="AS57" s="28" t="s">
+        <v>606</v>
+      </c>
+      <c r="AT57" s="29"/>
+      <c r="AU57" s="29"/>
+      <c r="AV57" s="29"/>
+      <c r="AW57" s="29"/>
+      <c r="AX57" s="29"/>
+      <c r="AY57" s="29"/>
+      <c r="AZ57" s="29"/>
+      <c r="BA57" s="29"/>
+      <c r="BB57" s="29"/>
+      <c r="BC57" s="29"/>
+      <c r="BD57" s="29"/>
+    </row>
+    <row r="58" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A58" s="40" t="s">
+        <v>464</v>
+      </c>
+      <c r="V58" s="40" t="s">
+        <v>464</v>
+      </c>
+      <c r="AS58" s="40" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="59" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A59" s="31" t="s">
+        <v>759</v>
+      </c>
+      <c r="V59" s="31" t="s">
+        <v>760</v>
+      </c>
+      <c r="AS59" s="31" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="60" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A60" s="32" t="s">
+        <v>750</v>
+      </c>
+      <c r="V60" s="32" t="s">
+        <v>753</v>
+      </c>
+      <c r="AS60" s="32" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="61" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="V61" s="32" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="62" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A62" s="47" t="s">
+        <v>465</v>
+      </c>
+      <c r="B62" s="42"/>
+      <c r="C62" s="42"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="V62" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="W62" s="42"/>
+      <c r="X62" s="42"/>
+      <c r="Y62" s="42"/>
+      <c r="Z62" s="42"/>
+      <c r="AS62" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="AT62" s="42"/>
+      <c r="AU62" s="42"/>
+      <c r="AV62" s="42"/>
+      <c r="AW62" s="42"/>
+    </row>
+    <row r="63" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A63" s="38" t="s">
+        <v>466</v>
+      </c>
+      <c r="V63" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="AS63" s="17" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="64" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A64" s="33" t="s">
+        <v>467</v>
+      </c>
+      <c r="V64" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="AS64" s="33"/>
+    </row>
+    <row r="65" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A65" s="33"/>
+      <c r="V65" s="33"/>
+      <c r="AS65" s="17" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="66" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A66" s="38" t="s">
+        <v>468</v>
+      </c>
+      <c r="V66" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="AS66" s="17" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="67" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A67" s="33" t="s">
+        <v>469</v>
+      </c>
+      <c r="V67" s="33" t="s">
+        <v>541</v>
+      </c>
+      <c r="AS67" s="17" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="68" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A68" s="33"/>
+      <c r="V68" s="33"/>
+      <c r="AS68" s="33"/>
+    </row>
+    <row r="69" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A69" s="38" t="s">
+        <v>470</v>
+      </c>
+      <c r="V69" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="AS69" s="17" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="70" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A70" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="V70" s="33" t="s">
+        <v>543</v>
+      </c>
+      <c r="AS70" s="17" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="71" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="AS71" s="33"/>
+    </row>
+    <row r="72" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A72" s="38" t="s">
+        <v>471</v>
+      </c>
+      <c r="V72" s="19" t="s">
+        <v>544</v>
+      </c>
+      <c r="AS72" s="17" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="73" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A73" s="33" t="s">
+        <v>472</v>
+      </c>
+      <c r="V73" s="33" t="s">
+        <v>545</v>
+      </c>
+      <c r="AS73" s="17" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="74" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A74" s="33" t="s">
+        <v>473</v>
+      </c>
+      <c r="V74" s="33" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="75" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A75" s="33"/>
+      <c r="V75" s="33"/>
+      <c r="AS75" s="48" t="s">
+        <v>614</v>
+      </c>
+      <c r="AT75" s="42"/>
+      <c r="AU75" s="42"/>
+      <c r="AV75" s="42"/>
+      <c r="AW75" s="42"/>
+      <c r="AX75" s="42"/>
+      <c r="AY75" s="42"/>
+      <c r="AZ75" s="42"/>
+      <c r="BA75" s="42"/>
+      <c r="BB75" s="42"/>
+      <c r="BC75" s="42"/>
+      <c r="BD75" s="42"/>
+    </row>
+    <row r="76" spans="1:91" ht="21" x14ac:dyDescent="0.4">
+      <c r="A76" s="38" t="s">
+        <v>474</v>
+      </c>
+      <c r="V76" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="AS76" s="18" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="77" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A77" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="V77" s="33" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="78" spans="1:91" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="V78" s="33"/>
+      <c r="W78" s="30"/>
+      <c r="X78" s="30"/>
+      <c r="Y78" s="30"/>
+      <c r="Z78" s="30"/>
+      <c r="AA78" s="30"/>
+      <c r="AB78" s="30"/>
+      <c r="AC78" s="30"/>
+      <c r="AD78" s="30"/>
+      <c r="AE78" s="30"/>
+      <c r="AF78" s="30"/>
+      <c r="AG78" s="30"/>
+      <c r="AH78" s="30"/>
+      <c r="AI78" s="30"/>
+      <c r="AJ78" s="30"/>
+      <c r="AK78" s="30"/>
+      <c r="AL78" s="30"/>
+      <c r="AM78" s="30"/>
+      <c r="AN78" s="30"/>
+      <c r="AO78" s="30"/>
+      <c r="AP78" s="30"/>
+      <c r="AQ78" s="30"/>
+      <c r="AR78" s="30"/>
+      <c r="AS78" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="AT78" s="30"/>
+      <c r="AU78" s="30"/>
+      <c r="AV78" s="30"/>
+      <c r="AW78" s="30"/>
+      <c r="AX78" s="30"/>
+      <c r="AY78" s="30"/>
+      <c r="AZ78" s="30"/>
+      <c r="BA78" s="30"/>
+      <c r="BB78" s="30"/>
+      <c r="BC78" s="30"/>
+      <c r="BD78" s="30"/>
+      <c r="BE78" s="30"/>
+      <c r="BF78" s="30"/>
+      <c r="BG78" s="30"/>
+      <c r="BH78" s="30"/>
+      <c r="BK78" s="30"/>
+      <c r="BL78" s="30"/>
+      <c r="BM78" s="30"/>
+      <c r="BN78" s="30"/>
+      <c r="BO78" s="30"/>
+      <c r="BP78" s="30"/>
+      <c r="BQ78" s="30"/>
+      <c r="BZ78" s="30"/>
+      <c r="CA78" s="30"/>
+      <c r="CB78" s="30"/>
+      <c r="CC78" s="30"/>
+      <c r="CD78" s="30"/>
+      <c r="CE78" s="30"/>
+      <c r="CF78" s="30"/>
+      <c r="CG78" s="30"/>
+      <c r="CH78" s="30"/>
+      <c r="CI78" s="30"/>
+      <c r="CJ78" s="30"/>
+      <c r="CK78" s="30"/>
+      <c r="CL78" s="30"/>
+      <c r="CM78" s="30"/>
+    </row>
+    <row r="79" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A79" s="41" t="s">
+        <v>476</v>
+      </c>
+      <c r="B79" s="42"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="V79" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="AS79" s="33" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="80" spans="1:91" x14ac:dyDescent="0.25">
+      <c r="A80" s="18" t="s">
+        <v>772</v>
+      </c>
+      <c r="V80" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="AS80" s="33"/>
+    </row>
+    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A81" s="20" t="s">
+        <v>751</v>
+      </c>
+      <c r="V81" s="33" t="s">
+        <v>549</v>
+      </c>
+      <c r="AS81" s="33" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="82" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="V82" s="33" t="s">
+        <v>550</v>
+      </c>
+      <c r="AS82" s="33"/>
+    </row>
+    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A83" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="V83" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="AS83" s="33" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A84" s="33" t="s">
+        <v>478</v>
+      </c>
+      <c r="V84" s="33" t="s">
+        <v>551</v>
+      </c>
+      <c r="AS84" s="33" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A85" s="33" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A86" s="33" t="s">
+        <v>480</v>
+      </c>
+      <c r="V86" s="41" t="s">
+        <v>552</v>
+      </c>
+      <c r="W86" s="42"/>
+      <c r="X86" s="42"/>
+      <c r="Y86" s="42"/>
+      <c r="Z86" s="42"/>
+      <c r="AA86" s="42"/>
+      <c r="AB86" s="42"/>
+      <c r="AC86" s="42"/>
+      <c r="AD86" s="42"/>
+      <c r="AE86" s="42"/>
+      <c r="AS86" s="48" t="s">
+        <v>618</v>
+      </c>
+      <c r="AT86" s="49"/>
+      <c r="AU86" s="49"/>
+      <c r="AV86" s="49"/>
+      <c r="AW86" s="49"/>
+      <c r="AX86" s="49"/>
+      <c r="AY86" s="49"/>
+      <c r="AZ86" s="49"/>
+    </row>
+    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A87" s="33"/>
+      <c r="V87" s="18" t="s">
+        <v>776</v>
+      </c>
+      <c r="AS87" s="18" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A88" s="33" t="s">
+        <v>481</v>
+      </c>
+      <c r="AS88" s="18" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A89" s="33" t="s">
+        <v>482</v>
+      </c>
+      <c r="V89" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="AS89" s="33" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A90" s="33" t="s">
+        <v>483</v>
+      </c>
+      <c r="V90" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="AS90" s="33" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A91" s="33"/>
+      <c r="V91" s="33"/>
+      <c r="AS91" s="33"/>
+    </row>
+    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A92" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="V92" s="33" t="s">
+        <v>554</v>
+      </c>
+      <c r="AS92" s="33" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A93" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="V93" s="33" t="s">
+        <v>555</v>
+      </c>
+      <c r="AS93" s="33" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="V94" s="33" t="s">
+        <v>556</v>
+      </c>
+      <c r="AS94" s="17" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A95" s="41" t="s">
+        <v>486</v>
+      </c>
+      <c r="B95" s="42"/>
+      <c r="C95" s="42"/>
+      <c r="D95" s="42"/>
+      <c r="E95" s="42"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="42"/>
+      <c r="I95" s="42"/>
+      <c r="V95" s="33"/>
+      <c r="AS95" s="17" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A96" s="18" t="s">
+        <v>773</v>
+      </c>
+      <c r="B96" s="20"/>
+      <c r="C96" s="20"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+      <c r="F96" s="20"/>
+      <c r="G96" s="20"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="20"/>
+      <c r="J96" s="20"/>
+      <c r="K96" s="20"/>
+      <c r="L96" s="20"/>
+      <c r="M96" s="20"/>
+      <c r="N96" s="20"/>
+      <c r="O96" s="20"/>
+      <c r="P96" s="20"/>
+      <c r="Q96" s="20"/>
+      <c r="V96" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="AS96" s="33" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="97" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A97" s="30" t="s">
+        <v>752</v>
+      </c>
+      <c r="V97" s="33" t="s">
+        <v>557</v>
+      </c>
+      <c r="AS97" s="33" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="98" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A98" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="V98" s="33" t="s">
+        <v>558</v>
+      </c>
+      <c r="AS98" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="99" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A99" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="V99" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="AS99" s="33"/>
+    </row>
+    <row r="100" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A100" s="33"/>
+      <c r="V100" s="33" t="s">
+        <v>559</v>
+      </c>
+      <c r="AS100" s="17" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="101" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A101" s="33" t="s">
+        <v>488</v>
+      </c>
+      <c r="V101" s="33"/>
+      <c r="AS101" s="33" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="102" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A102" s="33" t="s">
+        <v>489</v>
+      </c>
+      <c r="V102" s="33" t="s">
+        <v>560</v>
+      </c>
+      <c r="AS102" s="33"/>
+    </row>
+    <row r="103" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A103" s="33"/>
+      <c r="V103" s="33" t="s">
+        <v>553</v>
+      </c>
+      <c r="AS103" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="AT103" s="20"/>
+    </row>
+    <row r="104" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A104" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="V104" s="18" t="s">
+        <v>777</v>
+      </c>
+      <c r="AS104" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="AT104" s="20"/>
+    </row>
+    <row r="105" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A105" s="33" t="s">
+        <v>491</v>
+      </c>
+      <c r="V105" s="20" t="s">
+        <v>755</v>
+      </c>
+      <c r="AS105" s="19" t="s">
+        <v>296</v>
+      </c>
+      <c r="AT105" s="20"/>
+    </row>
+    <row r="106" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A106" s="33"/>
+      <c r="AS106" s="19" t="s">
+        <v>625</v>
+      </c>
+      <c r="AT106" s="20"/>
+    </row>
+    <row r="107" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A107" s="33" t="s">
+        <v>492</v>
+      </c>
+      <c r="V107" s="41" t="s">
+        <v>561</v>
+      </c>
+      <c r="W107" s="42"/>
+      <c r="X107" s="42"/>
+      <c r="Y107" s="42"/>
+      <c r="Z107" s="42"/>
+      <c r="AA107" s="42"/>
+      <c r="AB107" s="42"/>
+      <c r="AC107" s="42"/>
+      <c r="AD107" s="42"/>
+      <c r="AE107" s="42"/>
+      <c r="AS107" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="AT107" s="20"/>
+    </row>
+    <row r="108" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A108" s="33" t="s">
+        <v>493</v>
+      </c>
+      <c r="V108" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="AS108" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="AT108" s="20"/>
+    </row>
+    <row r="109" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A109" s="33" t="s">
+        <v>494</v>
+      </c>
+      <c r="V109" s="19" t="s">
+        <v>562</v>
+      </c>
+      <c r="AS109" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT109" s="20"/>
+    </row>
+    <row r="110" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A110" s="33" t="s">
+        <v>495</v>
+      </c>
+      <c r="V110" s="19"/>
+    </row>
+    <row r="111" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="A111" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="V111" s="19" t="s">
+        <v>554</v>
+      </c>
+      <c r="AS111" s="50" t="s">
+        <v>627</v>
+      </c>
+      <c r="AT111" s="42"/>
+      <c r="AU111" s="42"/>
+      <c r="AV111" s="42"/>
+      <c r="AW111" s="42"/>
+      <c r="AX111" s="42"/>
+    </row>
+    <row r="112" spans="1:50" x14ac:dyDescent="0.25">
+      <c r="V112" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="AS112" s="33" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="113" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A113" s="41" t="s">
+        <v>496</v>
+      </c>
+      <c r="B113" s="42"/>
+      <c r="C113" s="42"/>
+      <c r="D113" s="42"/>
+      <c r="E113" s="42"/>
+      <c r="F113" s="42"/>
+      <c r="G113" s="42"/>
+      <c r="H113" s="42"/>
+      <c r="I113" s="42"/>
+      <c r="J113" s="42"/>
+      <c r="K113" s="42"/>
+      <c r="V113" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="AS113" s="33"/>
+    </row>
+    <row r="114" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A114" s="18" t="s">
+        <v>774</v>
+      </c>
+      <c r="AS114" s="33" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="115" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A115" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="V115" s="18" t="s">
+        <v>778</v>
+      </c>
+      <c r="AS115" s="33" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="116" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A116" s="33"/>
+      <c r="AS116" s="33" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="117" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A117" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="V117" s="41" t="s">
+        <v>565</v>
+      </c>
+      <c r="W117" s="42"/>
+      <c r="X117" s="42"/>
+      <c r="Y117" s="42"/>
+      <c r="Z117" s="42"/>
+      <c r="AA117" s="42"/>
+      <c r="AB117" s="42"/>
+      <c r="AS117" s="33" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="118" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A118" s="33" t="s">
+        <v>488</v>
+      </c>
+      <c r="V118" s="19" t="s">
+        <v>566</v>
+      </c>
+      <c r="AS118" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="119" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A119" s="33"/>
+      <c r="V119" s="19" t="s">
+        <v>567</v>
+      </c>
+      <c r="AS119" s="33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="120" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A120" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="V120" s="33"/>
+    </row>
+    <row r="121" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A121" s="33" t="s">
+        <v>480</v>
+      </c>
+      <c r="V121" s="33" t="s">
+        <v>568</v>
+      </c>
+      <c r="AS121" s="41" t="s">
+        <v>633</v>
+      </c>
+      <c r="AT121" s="42"/>
+      <c r="AU121" s="42"/>
+      <c r="AV121" s="42"/>
+      <c r="AW121" s="42"/>
+      <c r="AX121" s="42"/>
+      <c r="AY121" s="42"/>
+      <c r="AZ121" s="42"/>
+      <c r="BA121" s="42"/>
+      <c r="BB121" s="42"/>
+      <c r="BC121" s="42"/>
+    </row>
+    <row r="122" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A122" s="33"/>
+      <c r="V122" s="33" t="s">
+        <v>569</v>
+      </c>
+      <c r="AS122" s="33" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="123" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A123" s="33" t="s">
+        <v>499</v>
+      </c>
+      <c r="V123" s="33" t="s">
+        <v>570</v>
+      </c>
+      <c r="AS123" s="33" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="124" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A124" s="33" t="s">
+        <v>500</v>
+      </c>
+      <c r="V124" s="33"/>
+      <c r="AS124" s="33" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="125" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A125" s="33" t="s">
+        <v>501</v>
+      </c>
+      <c r="V125" s="19" t="s">
+        <v>571</v>
+      </c>
+      <c r="AS125" s="33"/>
+    </row>
+    <row r="126" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A126" s="33" t="s">
+        <v>502</v>
+      </c>
+      <c r="V126" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="AS126" s="33" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="127" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="AS127" s="33" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="128" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A128" s="41" t="s">
+        <v>503</v>
+      </c>
+      <c r="B128" s="42"/>
+      <c r="C128" s="42"/>
+      <c r="D128" s="42"/>
+      <c r="E128" s="42"/>
+      <c r="F128" s="42"/>
+      <c r="G128" s="42"/>
+      <c r="H128" s="42"/>
+      <c r="V128" s="41" t="s">
+        <v>573</v>
+      </c>
+      <c r="W128" s="42"/>
+      <c r="X128" s="42"/>
+      <c r="Y128" s="42"/>
+      <c r="Z128" s="42"/>
+      <c r="AA128" s="42"/>
+      <c r="AB128" s="42"/>
+      <c r="AC128" s="42"/>
+      <c r="AD128" s="42"/>
+      <c r="AE128" s="42"/>
+      <c r="AF128" s="42"/>
+      <c r="AG128" s="42"/>
+      <c r="AS128" s="33"/>
+    </row>
+    <row r="129" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A129" s="33" t="s">
+        <v>504</v>
+      </c>
+      <c r="V129" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="AS129" s="33" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="130" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A130" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="V130" s="33" t="s">
+        <v>574</v>
+      </c>
+      <c r="AS130" s="33" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="131" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A131" s="33"/>
+      <c r="V131" s="33"/>
+      <c r="AS131" s="18" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="132" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A132" s="33" t="s">
+        <v>506</v>
+      </c>
+      <c r="V132" s="19" t="s">
+        <v>575</v>
+      </c>
+      <c r="AS132" s="20" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="133" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A133" s="33" t="s">
+        <v>507</v>
+      </c>
+      <c r="V133" s="33" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="134" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A134" s="33"/>
+      <c r="V134" s="33" t="s">
+        <v>576</v>
+      </c>
+      <c r="AS134" s="41" t="s">
+        <v>641</v>
+      </c>
+      <c r="AT134" s="42"/>
+      <c r="AU134" s="42"/>
+      <c r="AV134" s="42"/>
+      <c r="AW134" s="42"/>
+      <c r="AX134" s="42"/>
+      <c r="AY134" s="42"/>
+      <c r="AZ134" s="42"/>
+    </row>
+    <row r="135" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A135" s="33" t="s">
+        <v>508</v>
+      </c>
+      <c r="V135" s="33"/>
+      <c r="AS135" s="33" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="136" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A136" s="33" t="s">
+        <v>509</v>
+      </c>
+      <c r="V136" s="19" t="s">
+        <v>577</v>
+      </c>
+      <c r="AS136" s="33"/>
+    </row>
+    <row r="137" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A137" s="33" t="s">
+        <v>510</v>
+      </c>
+      <c r="V137" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="AS137" s="33" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="138" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AS138" s="33" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="139" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A139" s="41" t="s">
+        <v>511</v>
+      </c>
+      <c r="B139" s="42"/>
+      <c r="C139" s="42"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42"/>
+      <c r="F139" s="42"/>
+      <c r="G139" s="42"/>
+      <c r="H139" s="42"/>
+      <c r="I139" s="42"/>
+      <c r="V139" s="41" t="s">
+        <v>579</v>
+      </c>
+      <c r="W139" s="42"/>
+      <c r="X139" s="42"/>
+      <c r="Y139" s="42"/>
+      <c r="Z139" s="42"/>
+      <c r="AA139" s="42"/>
+      <c r="AB139" s="42"/>
+      <c r="AC139" s="42"/>
+      <c r="AD139" s="42"/>
+      <c r="AE139" s="42"/>
+      <c r="AF139" s="42"/>
+      <c r="AS139" s="33"/>
+    </row>
+    <row r="140" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A140" s="33" t="s">
+        <v>512</v>
+      </c>
+      <c r="V140" s="33" t="s">
+        <v>580</v>
+      </c>
+      <c r="AS140" s="33" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="141" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A141" s="33"/>
+      <c r="V141" s="33" t="s">
+        <v>581</v>
+      </c>
+      <c r="AS141" s="33"/>
+    </row>
+    <row r="142" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A142" s="33" t="s">
+        <v>513</v>
+      </c>
+      <c r="V142" s="33"/>
+      <c r="AS142" s="33" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="143" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A143" s="33" t="s">
+        <v>514</v>
+      </c>
+      <c r="V143" s="17" t="s">
+        <v>582</v>
+      </c>
+      <c r="AS143" s="33" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="144" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A144" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="V144" s="33" t="s">
+        <v>583</v>
+      </c>
+      <c r="AS144" s="33" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="145" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A145" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="V145" s="33" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="146" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A146" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="V146" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="AS146" s="41" t="s">
+        <v>646</v>
+      </c>
+      <c r="AT146" s="42"/>
+      <c r="AU146" s="42"/>
+      <c r="AV146" s="42"/>
+      <c r="AW146" s="42"/>
+      <c r="AX146" s="42"/>
+      <c r="AY146" s="42"/>
+    </row>
+    <row r="147" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A147" s="33"/>
+      <c r="V147" s="33"/>
+      <c r="AS147" s="33" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="148" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A148" s="33" t="s">
+        <v>516</v>
+      </c>
+      <c r="V148" s="19" t="s">
+        <v>585</v>
+      </c>
+      <c r="AS148" s="33" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="149" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A149" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="V149" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="AS149" s="33"/>
+    </row>
+    <row r="150" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A150" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="V150" s="33" t="s">
+        <v>587</v>
+      </c>
+      <c r="AS150" s="19" t="s">
+        <v>649</v>
+      </c>
+      <c r="AT150" s="20"/>
+    </row>
+    <row r="151" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="V151" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="AS151" s="19" t="s">
+        <v>650</v>
+      </c>
+      <c r="AT151" s="20"/>
+    </row>
+    <row r="152" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A152" s="46" t="s">
+        <v>775</v>
+      </c>
+      <c r="B152" s="42"/>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="42"/>
+      <c r="F152" s="42"/>
+      <c r="G152" s="42"/>
+      <c r="H152" s="42"/>
+      <c r="I152" s="42"/>
+      <c r="J152" s="42"/>
+      <c r="K152" s="42"/>
+      <c r="L152" s="42"/>
+      <c r="AS152" s="19"/>
+      <c r="AT152" s="20"/>
+    </row>
+    <row r="153" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A153" s="33" t="s">
+        <v>517</v>
+      </c>
+      <c r="V153" s="41" t="s">
+        <v>588</v>
+      </c>
+      <c r="W153" s="42"/>
+      <c r="X153" s="42"/>
+      <c r="Y153" s="42"/>
+      <c r="Z153" s="42"/>
+      <c r="AA153" s="42"/>
+      <c r="AB153" s="42"/>
+      <c r="AC153" s="42"/>
+      <c r="AS153" s="19" t="s">
+        <v>651</v>
+      </c>
+      <c r="AT153" s="20"/>
+    </row>
+    <row r="154" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A154" s="33" t="s">
+        <v>518</v>
+      </c>
+      <c r="V154" s="19" t="s">
+        <v>580</v>
+      </c>
+      <c r="AS154" s="19"/>
+      <c r="AT154" s="20"/>
+    </row>
+    <row r="155" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A155" s="33" t="s">
+        <v>519</v>
+      </c>
+      <c r="V155" s="19" t="s">
+        <v>581</v>
+      </c>
+      <c r="AS155" s="19" t="s">
+        <v>652</v>
+      </c>
+      <c r="AT155" s="20"/>
+    </row>
+    <row r="156" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A156" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="V156" s="19"/>
+      <c r="AS156" s="19" t="s">
+        <v>653</v>
+      </c>
+      <c r="AT156" s="20"/>
+    </row>
+    <row r="157" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A157" s="33"/>
+      <c r="V157" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="AS157" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AT157" s="20"/>
+    </row>
+    <row r="158" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A158" s="19" t="s">
+        <v>520</v>
+      </c>
+      <c r="V158" s="19" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="159" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A159" s="19" t="s">
+        <v>521</v>
+      </c>
+      <c r="AS159" s="41" t="s">
+        <v>654</v>
+      </c>
+      <c r="AT159" s="42"/>
+      <c r="AU159" s="42"/>
+      <c r="AV159" s="42"/>
+      <c r="AW159" s="42"/>
+      <c r="AX159" s="42"/>
+      <c r="AY159" s="42"/>
+      <c r="AZ159" s="42"/>
+    </row>
+    <row r="160" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A160" s="19" t="s">
         <v>522</v>
       </c>
-      <c r="V3" s="18" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A4" s="20" t="s">
+      <c r="V160" s="23" t="s">
+        <v>589</v>
+      </c>
+      <c r="W160" s="42"/>
+      <c r="X160" s="42"/>
+      <c r="Y160" s="42"/>
+      <c r="Z160" s="42"/>
+      <c r="AA160" s="42"/>
+      <c r="AB160" s="42"/>
+      <c r="AC160" s="42"/>
+      <c r="AD160" s="42"/>
+      <c r="AE160" s="42"/>
+      <c r="AF160" s="42"/>
+      <c r="AG160" s="42"/>
+      <c r="AH160" s="42"/>
+      <c r="AI160" s="42"/>
+      <c r="AS160" s="33" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="161" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A161" s="19" t="s">
         <v>523</v>
       </c>
-      <c r="V4" s="11" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="V5" s="11" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="V6" s="11" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="V7" s="11"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="V8" s="11" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="V9" s="11" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="V10" s="11" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="V11" s="11"/>
-    </row>
-    <row r="12" spans="1:30" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="V12" s="11" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="V13" s="11" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
-      <c r="V14" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30" ht="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="V15" s="11" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="V16" s="11" t="s">
+      <c r="V161" s="18" t="s">
+        <v>779</v>
+      </c>
+      <c r="AS161" s="33" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="162" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="AS162" s="33"/>
+    </row>
+    <row r="163" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A163" s="41" t="s">
+        <v>524</v>
+      </c>
+      <c r="B163" s="42"/>
+      <c r="C163" s="42"/>
+      <c r="D163" s="42"/>
+      <c r="E163" s="42"/>
+      <c r="F163" s="42"/>
+      <c r="G163" s="42"/>
+      <c r="H163" s="42"/>
+      <c r="V163" s="33" t="s">
+        <v>590</v>
+      </c>
+      <c r="AS163" s="33" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="164" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A164" s="33" t="s">
+        <v>504</v>
+      </c>
+      <c r="V164" s="33"/>
+      <c r="AS164" s="33"/>
+    </row>
+    <row r="165" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A165" s="33" t="s">
+        <v>505</v>
+      </c>
+      <c r="V165" s="33" t="s">
+        <v>540</v>
+      </c>
+      <c r="AS165" s="33" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="166" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A166" s="33"/>
+      <c r="V166" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="AS166" s="33" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="167" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A167" s="33" t="s">
+        <v>525</v>
+      </c>
+      <c r="V167" s="33"/>
+      <c r="AS167" s="33"/>
+    </row>
+    <row r="168" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A168" s="33" t="s">
+        <v>526</v>
+      </c>
+      <c r="V168" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="AS168" s="33" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="169" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A169" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="AS169" s="33" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="170" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="V170" s="41" t="s">
+        <v>593</v>
+      </c>
+      <c r="W170" s="42"/>
+      <c r="X170" s="42"/>
+      <c r="Y170" s="42"/>
+      <c r="Z170" s="42"/>
+      <c r="AA170" s="42"/>
+      <c r="AB170" s="42"/>
+    </row>
+    <row r="171" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A171" s="41" t="s">
+        <v>528</v>
+      </c>
+      <c r="B171" s="42"/>
+      <c r="C171" s="42"/>
+      <c r="D171" s="42"/>
+      <c r="E171" s="42"/>
+      <c r="F171" s="42"/>
+      <c r="G171" s="42"/>
+      <c r="H171" s="42"/>
+      <c r="I171" s="42"/>
+      <c r="V171" s="18" t="s">
+        <v>780</v>
+      </c>
+      <c r="AS171" s="51" t="s">
+        <v>659</v>
+      </c>
+      <c r="AT171" s="29"/>
+      <c r="AU171" s="29"/>
+      <c r="AV171" s="29"/>
+      <c r="AW171" s="29"/>
+      <c r="AX171" s="29"/>
+      <c r="AY171" s="29"/>
+      <c r="AZ171" s="29"/>
+      <c r="BA171" s="29"/>
+      <c r="BB171" s="29"/>
+      <c r="BC171" s="29"/>
+    </row>
+    <row r="172" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A172" s="33" t="s">
+        <v>529</v>
+      </c>
+      <c r="AS172" s="18" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="173" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A173" s="33"/>
+      <c r="V173" s="33" t="s">
+        <v>594</v>
+      </c>
+      <c r="AS173" s="33" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="174" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A174" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="V174" s="33" t="s">
+        <v>595</v>
+      </c>
+      <c r="AS174" s="33" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="175" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A175" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="V175" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="AS175" s="33" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="176" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A176" s="33"/>
+      <c r="V176" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="AS176" s="11" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="177" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A177" s="33" t="s">
+        <v>532</v>
+      </c>
+      <c r="V177" s="33"/>
+      <c r="AS177" s="33" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="178" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A178" s="33" t="s">
+        <v>533</v>
+      </c>
+      <c r="V178" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="AS178" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="179" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A179" s="33"/>
+      <c r="V179" s="33" t="s">
+        <v>598</v>
+      </c>
+      <c r="AS179" s="33" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="180" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A180" s="33" t="s">
+        <v>534</v>
+      </c>
+      <c r="V180" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="AS180" s="33" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="181" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A181" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="V181" s="33"/>
+      <c r="AS181" s="33"/>
+    </row>
+    <row r="182" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A182" s="33" t="s">
+        <v>494</v>
+      </c>
+      <c r="V182" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="AS182" s="33" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="183" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A183" s="33" t="s">
+        <v>536</v>
+      </c>
+      <c r="V183" s="33" t="s">
+        <v>601</v>
+      </c>
+      <c r="AS183" s="33" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="184" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A184" s="33" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="17" spans="1:59" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="V17" s="11" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="V18" s="11" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="19" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="V19" s="11" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A20" s="21" t="s">
-        <v>518</v>
-      </c>
-      <c r="V20" s="11" t="s">
+      <c r="V184" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="AS184" s="33"/>
+    </row>
+    <row r="185" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A185" s="33"/>
+      <c r="V185" s="33"/>
+      <c r="AS185" s="33" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="186" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A186" s="33" t="s">
+        <v>537</v>
+      </c>
+      <c r="V186" s="33" t="s">
+        <v>603</v>
+      </c>
+      <c r="AS186" s="33" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="187" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="V187" s="33" t="s">
+        <v>604</v>
+      </c>
+      <c r="AS187" s="33" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="188" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="V188" s="33"/>
+      <c r="AS188" s="33" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="189" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="V189" s="17" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="190" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="V190" s="34" t="s">
+        <v>749</v>
+      </c>
+      <c r="AS190" s="50" t="s">
+        <v>673</v>
+      </c>
+      <c r="AT190" s="42"/>
+      <c r="AU190" s="42"/>
+      <c r="AV190" s="42"/>
+      <c r="AW190" s="42"/>
+      <c r="AX190" s="42"/>
+      <c r="AY190" s="42"/>
+      <c r="AZ190" s="42"/>
+      <c r="BA190" s="42"/>
+      <c r="BB190" s="42"/>
+      <c r="BC190" s="42"/>
+      <c r="BD190" s="42"/>
+    </row>
+    <row r="191" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="AS191" s="33" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="192" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A192" s="28" t="s">
+        <v>300</v>
+      </c>
+      <c r="B192" s="29"/>
+      <c r="C192" s="29"/>
+      <c r="D192" s="29"/>
+      <c r="E192" s="29"/>
+      <c r="F192" s="29"/>
+      <c r="G192" s="29"/>
+      <c r="H192" s="29"/>
+      <c r="I192" s="29"/>
+      <c r="J192" s="29"/>
+      <c r="K192" s="29"/>
+      <c r="AS192" s="33" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="193" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A193" s="31" t="s">
+        <v>454</v>
+      </c>
+      <c r="AS193" s="33" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="194" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AS194" s="33" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="195" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A195" s="38" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS195" s="33" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="196" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A196" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="AS196" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="197" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A197" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AS197" s="33" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="198" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A198" s="38" t="s">
+        <v>304</v>
+      </c>
+      <c r="AS198" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="199" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A199" s="33"/>
+      <c r="AS199" s="33"/>
+    </row>
+    <row r="200" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A200" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="AS200" s="33" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="201" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A201" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="AS201" s="33" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="202" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A202" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="AS202" s="33"/>
+    </row>
+    <row r="203" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A203" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="AS203" s="33" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="204" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AS204" s="33" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="205" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A205" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="AS205" s="33"/>
+    </row>
+    <row r="206" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A206" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="AS206" s="33" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="207" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A207" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="AS207" s="33" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="208" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A208" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="AS208" s="33" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="209" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A209" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="AS209" s="33" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="210" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A210" s="33"/>
+      <c r="AS210" s="33"/>
+    </row>
+    <row r="211" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A211" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="AS211" s="33" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="212" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A212" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="AS212" s="33" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="213" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A213" s="39"/>
+      <c r="AS213" s="33" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="214" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A214" s="35" t="s">
+        <v>746</v>
+      </c>
+      <c r="AS214" s="33" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="21" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A21" s="21" t="s">
-        <v>519</v>
-      </c>
-      <c r="V21" s="11" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A22" s="21" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="23" spans="1:59" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:59" s="14" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="U25" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AK25" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="AL25" s="16"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="16"/>
-      <c r="AP25" s="16"/>
-      <c r="AQ25" s="16"/>
-      <c r="AR25" s="16"/>
-      <c r="AZ25" s="15" t="s">
-        <v>275</v>
-      </c>
-      <c r="BA25" s="16"/>
-      <c r="BB25" s="16"/>
-      <c r="BC25" s="16"/>
-      <c r="BD25" s="16"/>
-      <c r="BE25" s="16"/>
-      <c r="BF25" s="16"/>
-      <c r="BG25" s="16"/>
-    </row>
-    <row r="26" spans="1:59" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
-        <v>525</v>
-      </c>
-      <c r="U26" s="18" t="s">
-        <v>527</v>
-      </c>
-      <c r="AK26" s="19" t="s">
-        <v>264</v>
-      </c>
-      <c r="AZ26" s="18" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A27" s="20" t="s">
-        <v>524</v>
-      </c>
-      <c r="U27" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="AK27" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AZ27" s="20" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="U28" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="AK28" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ28" s="11" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A29" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="AK29" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="AZ29" s="11" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A30" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="U30" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="AK30" s="11"/>
-      <c r="AZ30" s="11" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A31" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="U31" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="AK31" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="AZ31" s="11" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.2">
-      <c r="A32" s="11" t="s">
+    <row r="215" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A215" s="34" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="216" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A216" s="39" t="s">
+        <v>316</v>
+      </c>
+      <c r="AS216" s="41" t="s">
+        <v>684</v>
+      </c>
+      <c r="AT216" s="42"/>
+      <c r="AU216" s="42"/>
+      <c r="AV216" s="42"/>
+      <c r="AW216" s="42"/>
+      <c r="AX216" s="42"/>
+      <c r="AY216" s="42"/>
+      <c r="AZ216" s="42"/>
+    </row>
+    <row r="217" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A217" s="39" t="s">
+        <v>747</v>
+      </c>
+      <c r="AS217" s="33" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="218" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AS218" s="33" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="219" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A219" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29"/>
+      <c r="D219" s="29"/>
+      <c r="E219" s="29"/>
+      <c r="AS219" s="33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="220" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A220" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="AS220" s="33" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="221" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A221" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="AS221" s="33" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="222" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AS222" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="223" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A223" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="AS223" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="224" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A224" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="AS224" s="33" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="225" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A225" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="AS225" s="33" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="226" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A226" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="AS226" s="33" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="227" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A227" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="AS227" s="33" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="228" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A228" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="AS228" s="33" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="229" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A229" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="AS229" s="33" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="230" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A230" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS230" s="33" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="231" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A231" s="33"/>
+      <c r="AS231" s="33" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="232" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A232" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="AS232" s="33" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="233" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A233" s="33" t="s">
+        <v>325</v>
+      </c>
+      <c r="AS233" s="33" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="234" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A234" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="AQ234" s="32"/>
+      <c r="AR234" s="32"/>
+      <c r="AS234" s="33" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="235" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A235" s="33" t="s">
+        <v>327</v>
+      </c>
+      <c r="AS235" s="33" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="236" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A236" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS236" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="237" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A237" s="33"/>
+      <c r="AS237" s="33" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="238" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A238" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="AS238" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="239" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A239" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="AS239" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="240" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A240" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="AS240" s="33"/>
+    </row>
+    <row r="241" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A241" s="33" t="s">
+        <v>331</v>
+      </c>
+      <c r="AS241" s="33" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="242" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A242" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="AS242" s="33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="243" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A243" s="33" t="s">
+        <v>332</v>
+      </c>
+      <c r="AS243" s="33" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="244" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A244" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="AS244" s="33" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="245" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A245" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="AS245" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="246" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A246" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS246" s="33"/>
+    </row>
+    <row r="247" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AS247" s="33" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="248" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A248" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS248" s="33" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="249" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A249" s="39" t="s">
+        <v>335</v>
+      </c>
+      <c r="AS249" s="33"/>
+    </row>
+    <row r="250" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A250" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="AS250" s="33" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="251" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A251" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="AS251" s="33" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="252" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A252" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="AS252" s="33" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="253" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A253" s="39" t="s">
+        <v>339</v>
+      </c>
+      <c r="AS253" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="254" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AS254" s="33" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="255" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A255" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="AS255" s="33" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="256" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A256" s="33" t="s">
+        <v>341</v>
+      </c>
+      <c r="AS256" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="257" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A257" s="33" t="s">
+        <v>342</v>
+      </c>
+      <c r="AS257" s="33" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="258" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A258" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="AS258" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="U32" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="AK32" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="AZ32" s="11"/>
-    </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A33" s="11"/>
-      <c r="U33" s="11"/>
-      <c r="AK33" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="AZ33" s="11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A34" s="11" t="s">
-        <v>244</v>
-      </c>
-      <c r="U34" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="AK34" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="AZ34" s="11" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="U35" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="AK35" s="11" t="s">
+    </row>
+    <row r="259" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A259" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS259" s="33"/>
+    </row>
+    <row r="260" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A260" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="AS260" s="33" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="261" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A261" s="31" t="s">
+        <v>748</v>
+      </c>
+      <c r="B261" s="32"/>
+      <c r="C261" s="32"/>
+      <c r="D261" s="32"/>
+      <c r="E261" s="32"/>
+      <c r="F261" s="32"/>
+      <c r="G261" s="32"/>
+      <c r="H261" s="32"/>
+      <c r="I261" s="32"/>
+      <c r="J261" s="32"/>
+      <c r="K261" s="32"/>
+      <c r="L261" s="32"/>
+      <c r="AS261" s="33" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="263" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS263" s="41" t="s">
+        <v>714</v>
+      </c>
+      <c r="AT263" s="42"/>
+      <c r="AU263" s="42"/>
+      <c r="AV263" s="42"/>
+      <c r="AW263" s="42"/>
+      <c r="AX263" s="42"/>
+      <c r="AY263" s="42"/>
+      <c r="AZ263" s="42"/>
+      <c r="BA263" s="42"/>
+      <c r="BB263" s="42"/>
+    </row>
+    <row r="264" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS264" s="33" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="265" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS265" s="33" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="266" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS266" s="33" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="267" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS267" s="33" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="268" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS268" s="33" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="269" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS269" s="33" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="270" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS270" s="33" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="271" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS271" s="33" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="272" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="AS272" s="33" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="273" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS273" s="33" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="274" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS274" s="33" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="275" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS275" s="33" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="276" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS276" s="33" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="277" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS277" s="33" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="278" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS278" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="279" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS279" s="33" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="280" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS280" s="33" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="281" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS281" s="33" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="282" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS282" s="33" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="283" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS283" s="33" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="284" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS284" s="33" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="285" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS285" s="33" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="286" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS286" s="33" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="287" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS287" s="33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="288" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS288" s="33"/>
+    </row>
+    <row r="289" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS289" s="33" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="290" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS290" s="33" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="291" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS291" s="33"/>
+    </row>
+    <row r="292" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS292" s="33" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="293" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS293" s="33" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="294" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS294" s="33" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="295" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS295" s="33" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="296" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS296" s="33" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="297" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS297" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="AZ35" s="11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="U36" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="AK36" s="11"/>
-      <c r="AZ36" s="11" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="U37" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="AK37" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="AZ37" s="11"/>
-    </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="U38" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="AK38" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AZ38" s="11" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A39" s="11"/>
-      <c r="U39" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AK39" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="AZ39" s="11" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="AK40" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="AZ40" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="AK41" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="AZ41" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A42" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="AZ42" s="11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AZ43" s="11"/>
-    </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="AZ44" s="11" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="45" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="AZ45" s="11" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A46" s="21" t="s">
-        <v>251</v>
-      </c>
-      <c r="AZ46" s="11" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="A47" s="21" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="48" spans="1:52" ht="15" x14ac:dyDescent="0.25">
-      <c r="AZ48" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="49" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="AZ49" s="10" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="50" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="AZ50" s="10" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="51" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="AZ51" s="10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="52" spans="1:57" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:57" s="27" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="AE53" s="36" t="s">
-        <v>320</v>
-      </c>
-      <c r="AF53" s="29"/>
-      <c r="AG53" s="29"/>
-      <c r="AH53" s="29"/>
-      <c r="AI53" s="29"/>
-      <c r="BA53" s="36" t="s">
-        <v>344</v>
-      </c>
-      <c r="BB53" s="29"/>
-      <c r="BC53" s="29"/>
-      <c r="BD53" s="29"/>
-      <c r="BE53" s="29"/>
-    </row>
-    <row r="54" spans="1:57" ht="15" x14ac:dyDescent="0.25">
-      <c r="A54" s="18" t="s">
-        <v>553</v>
-      </c>
-      <c r="AE54" s="18" t="s">
-        <v>554</v>
-      </c>
-      <c r="BA54" s="18" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="55" spans="1:57" ht="15" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>531</v>
-      </c>
-      <c r="AE55" s="31" t="s">
-        <v>555</v>
-      </c>
-      <c r="BA55" s="18" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="56" spans="1:57" ht="15" x14ac:dyDescent="0.25">
-      <c r="A56" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="AE56" s="18" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="57" spans="1:57" ht="15" x14ac:dyDescent="0.25">
-      <c r="A57" s="18" t="s">
-        <v>533</v>
-      </c>
-      <c r="AE57" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="BA57" s="19" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="58" spans="1:57" ht="15" x14ac:dyDescent="0.25">
-      <c r="A58" s="31" t="s">
-        <v>532</v>
-      </c>
-      <c r="AE58" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="BA58" s="19" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="59" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A59" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="AE59" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="BA59" s="19"/>
-    </row>
-    <row r="60" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A60" s="11"/>
-      <c r="P60" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="AE60" s="11"/>
-      <c r="BA60" s="19" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="61" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A61" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="AE61" s="19" t="s">
-        <v>324</v>
-      </c>
-      <c r="BA61" s="11"/>
-    </row>
-    <row r="62" spans="1:57" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="AE62" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="BA62" s="11" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="63" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A63" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE63" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="BA63" s="11" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="64" spans="1:57" x14ac:dyDescent="0.2">
-      <c r="A64" s="11" t="s">
-        <v>296</v>
-      </c>
-      <c r="AE64" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="BA64" s="11" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A65" s="11"/>
-      <c r="AE65" s="11"/>
-      <c r="BA65" s="11" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="66" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A66" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="AE66" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="AF66" s="20"/>
-      <c r="BA66" s="11" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="67" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A67" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="AE67" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="AF67" s="20"/>
-      <c r="BA67" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A68" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="AE68" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="AF68" s="20"/>
-      <c r="BA68" s="11"/>
-    </row>
-    <row r="69" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A69" s="11"/>
-      <c r="AE69" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="AF69" s="20"/>
-      <c r="BA69" s="11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="70" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A70" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="AE70" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="AF70" s="20"/>
-      <c r="BA70" s="11" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="71" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A71" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="AE71" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="AF71" s="20"/>
-      <c r="BA71" s="11" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="72" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
-      <c r="AE72" s="11"/>
-      <c r="BA72" s="11" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="73" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A73" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="AE73" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="BA73" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="1:53" ht="15" x14ac:dyDescent="0.2">
-      <c r="A74" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="AE74" s="11" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="75" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="A75" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="AE75" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="BA75" s="7" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="76" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A76" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="BA76" s="11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="77" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="A77" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE77" s="35" t="s">
-        <v>335</v>
-      </c>
-      <c r="AF77" s="26"/>
-      <c r="AG77" s="26"/>
-      <c r="AH77" s="26"/>
-      <c r="AI77" s="26"/>
-      <c r="AJ77" s="26"/>
-      <c r="BA77" s="11" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="78" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A78" s="11"/>
-      <c r="AE78" s="11" t="s">
-        <v>336</v>
-      </c>
-      <c r="BA78" s="11" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="79" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A79" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="AE79" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="BA79" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="80" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A80" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE80" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="BA80" s="11"/>
-    </row>
-    <row r="81" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A81" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="AE81" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="BA81" s="11" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="82" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A82" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="BA82" s="11" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="83" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="AE83" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="AF83" s="26"/>
-      <c r="AG83" s="26"/>
-      <c r="AH83" s="26"/>
-      <c r="AI83" s="26"/>
-      <c r="BA83" s="11" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="84" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="A84" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="B84" s="33"/>
-      <c r="C84" s="33"/>
-      <c r="D84" s="33"/>
-      <c r="AE84" s="10" t="s">
-        <v>340</v>
-      </c>
-      <c r="BA84" s="11" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="85" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A85" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="AE85" s="10" t="s">
-        <v>341</v>
-      </c>
-      <c r="BA85" s="11" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="86" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A86" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="AE86" s="10" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="87" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="A87" s="34"/>
-      <c r="B87" s="34"/>
-      <c r="C87" s="34"/>
-      <c r="D87" s="34"/>
-      <c r="E87" s="34"/>
-      <c r="BA87" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="88" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="A88" s="32" t="s">
-        <v>313</v>
-      </c>
-      <c r="B88" s="33"/>
-      <c r="C88" s="33"/>
-      <c r="D88" s="33"/>
-      <c r="E88" s="33"/>
-      <c r="AE88" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF88" s="26"/>
-      <c r="AG88" s="26"/>
-      <c r="AH88" s="26"/>
-      <c r="AI88" s="26"/>
-      <c r="BA88" s="10" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="89" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A89" s="21" t="s">
-        <v>314</v>
-      </c>
-      <c r="AE89" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="BA89" s="10" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="90" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A90" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="AE90" s="21" t="s">
-        <v>556</v>
-      </c>
-      <c r="BA90" s="10" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="91" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A91" s="21" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="92" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A92" s="20"/>
-    </row>
-    <row r="93" spans="1:53" ht="15" x14ac:dyDescent="0.25">
-      <c r="A93" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="94" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A94" s="21" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="95" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A95" s="21" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="96" spans="1:53" x14ac:dyDescent="0.2">
-      <c r="A96" s="21" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="98" spans="1:35" ht="15" x14ac:dyDescent="0.2">
-      <c r="A98" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
-      <c r="D98" s="16"/>
-      <c r="E98" s="16"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="16"/>
-      <c r="H98" s="16"/>
-      <c r="I98" s="16"/>
-      <c r="J98" s="16"/>
-      <c r="K98" s="16"/>
-      <c r="AE98" s="15" t="s">
-        <v>386</v>
-      </c>
-      <c r="AF98" s="16"/>
-      <c r="AG98" s="16"/>
-      <c r="AH98" s="16"/>
-      <c r="AI98" s="16"/>
-    </row>
-    <row r="99" spans="1:35" ht="15" x14ac:dyDescent="0.25">
-      <c r="A99" s="18" t="s">
-        <v>539</v>
-      </c>
-      <c r="AE99" s="18" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="100" spans="1:35" ht="15" x14ac:dyDescent="0.25">
-      <c r="AE100" s="18" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="101" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A101" s="19" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="102" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A102" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="AE102" s="11" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="103" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A103" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="AE103" s="11" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="104" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A104" s="19" t="s">
-        <v>373</v>
-      </c>
-      <c r="AE104" s="11" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="105" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A105" s="11"/>
-      <c r="AE105" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="106" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A106" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="AE106" s="11" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="107" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A107" s="11" t="s">
-        <v>375</v>
-      </c>
-      <c r="AE107" s="11" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="108" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A108" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="AE108" s="11" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="109" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="A109" s="11" t="s">
-        <v>376</v>
-      </c>
-      <c r="AE109" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="110" spans="1:35" x14ac:dyDescent="0.2">
-      <c r="AE110" s="11"/>
-    </row>
-    <row r="111" spans="1:35" ht="15" x14ac:dyDescent="0.25">
-      <c r="A111" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="AE111" s="11" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="112" spans="1:35" ht="15" x14ac:dyDescent="0.2">
-      <c r="A112" s="8" t="s">
-        <v>378</v>
-      </c>
-      <c r="AE112" s="11" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="113" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A113" s="11" t="s">
-        <v>379</v>
-      </c>
-      <c r="AE113" s="11" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="114" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A114" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="AE114" s="11" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="115" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A115" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="AE115" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="116" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A116" s="11"/>
-      <c r="AE116" s="11"/>
-    </row>
-    <row r="117" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A117" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="AE117" s="11" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="118" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A118" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="AE118" s="11" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="119" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A119" s="10"/>
-      <c r="AE119" s="11" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="120" spans="1:31" ht="15" x14ac:dyDescent="0.2">
-      <c r="A120" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="AE120" s="11" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="121" spans="1:31" ht="15" x14ac:dyDescent="0.25">
-      <c r="A121" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="AE121" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="122" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A122" s="10" t="s">
-        <v>385</v>
-      </c>
-      <c r="AE122" s="11" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="123" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A123" s="10" t="s">
-        <v>517</v>
-      </c>
-      <c r="AE123" s="11" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="124" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AE124" s="11" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="125" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AE125" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="127" spans="1:31" ht="15" x14ac:dyDescent="0.25">
-      <c r="AE127" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="128" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="AE128" s="10" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="129" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE129" s="10" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="130" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE130" s="10" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="131" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE131" s="10" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="132" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE132" s="10" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="134" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE134" s="11" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="135" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE135" s="11" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="136" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE136" s="11" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="137" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE137" s="11" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="138" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE138" s="11" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="139" spans="31:48" x14ac:dyDescent="0.2">
-      <c r="AE139" s="11" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="140" spans="31:48" ht="15" x14ac:dyDescent="0.25">
-      <c r="AE140" s="18" t="s">
-        <v>540</v>
-      </c>
-      <c r="AF140" s="20"/>
-      <c r="AG140" s="20"/>
-      <c r="AH140" s="20"/>
-      <c r="AI140" s="20"/>
-      <c r="AJ140" s="20"/>
-      <c r="AK140" s="20"/>
-      <c r="AL140" s="20"/>
-      <c r="AM140" s="20"/>
-      <c r="AN140" s="20"/>
-      <c r="AO140" s="20"/>
-      <c r="AP140" s="20"/>
-      <c r="AQ140" s="20"/>
-      <c r="AR140" s="20"/>
-      <c r="AS140" s="20"/>
-      <c r="AT140" s="20"/>
-      <c r="AU140" s="20"/>
-      <c r="AV140" s="20"/>
-    </row>
-    <row r="169" s="20" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="298" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS298" s="33"/>
+    </row>
+    <row r="299" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS299" s="33" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="300" spans="45:45" x14ac:dyDescent="0.25">
+      <c r="AS300" s="33" t="s">
+        <v>737</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A190"/>
-  <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:BS117"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="3" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="12" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:71" s="14" customFormat="1" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="2" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A2" s="18" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="3" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A3" s="43" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="5" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="Q5" s="15" t="s">
+        <v>360</v>
+      </c>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AK5" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="AL5" s="16"/>
+      <c r="AM5" s="16"/>
+      <c r="AN5" s="16"/>
+      <c r="AO5" s="16"/>
+      <c r="BJ5" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="BK5" s="16"/>
+      <c r="BL5" s="16"/>
+      <c r="BM5" s="16"/>
+      <c r="BN5" s="16"/>
+      <c r="BO5" s="16"/>
+      <c r="BP5" s="16"/>
+      <c r="BQ5" s="16"/>
+      <c r="BR5" s="16"/>
+      <c r="BS5" s="16"/>
+    </row>
+    <row r="6" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>766</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>764</v>
+      </c>
+      <c r="AK6" s="18" t="s">
+        <v>769</v>
+      </c>
+      <c r="BJ6" s="7" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="7" spans="1:71" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>765</v>
+      </c>
+      <c r="AK7" s="20" t="s">
+        <v>768</v>
+      </c>
+      <c r="BJ7" s="9" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+        <v>347</v>
+      </c>
+      <c r="Q8" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="AK8" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="BJ8" s="11" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+      <c r="Q9" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="AK9" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="BJ9" s="11" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="Q10" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK10" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="BJ10" s="11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+        <v>349</v>
+      </c>
+      <c r="Q11" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="AK11" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="BJ11" s="11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="AK12" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="BJ12" s="11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+        <v>351</v>
+      </c>
+      <c r="Q13" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="AK13" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="BJ13" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+        <v>352</v>
+      </c>
+      <c r="Q14" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK14" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="BJ14" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+      <c r="Q15" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="AK15" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="BJ15" s="11" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="16" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="Q16" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="AK16" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="BJ16" s="11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+      <c r="Q17" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="AK17" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="BJ17" s="11" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+      <c r="Q18" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="AK18" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="BJ18" s="11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+      <c r="Q19" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="AK19" s="19" t="s">
+        <v>384</v>
+      </c>
+      <c r="BJ19" s="11" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="Q20" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="AK20" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="BJ20" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="Q21" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK21" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="BJ21" s="11" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q22" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="AK22" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="BJ22" s="11" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="Q23" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="AK23" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="BJ23" s="11" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="AK24" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="BJ24" s="11" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="AK25" s="11"/>
+      <c r="BJ25" s="11" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A26" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q26" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="AK26" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="BJ26" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q27" s="11"/>
+      <c r="AK27" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q28" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="AK28" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="BJ28" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q29" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="AK29" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="BJ29" s="10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q30" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="AK30" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="BJ30" s="10" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q31" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="AK31" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="BJ31" s="10" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="Q32" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="AK32" s="11"/>
+      <c r="BJ32" s="10" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="33" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK33" s="11" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="34" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="Q34" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="AK34" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="BJ34" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="35" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="Q35" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="AK35" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="BJ35" s="11" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="36" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="Q36" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="AK36" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="BJ36" s="11" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="37" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="Q37" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="AK37" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="BJ37" s="11" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="38" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK38" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="BJ38" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="39" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK39" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="BJ39" s="11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="40" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="BJ40" s="11" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="41" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK41" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="BJ41" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK42" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="BJ42" s="11" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="43" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK43" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="BJ43" s="11" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="44" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK44" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="BJ44" s="11" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="45" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="AK45" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="BJ45" s="11" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="46" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="BJ46" s="11" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="47" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="BJ47" s="11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="17:62" x14ac:dyDescent="0.25">
+      <c r="BJ48" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="49" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ49" s="11"/>
+    </row>
+    <row r="50" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ50" s="11" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
+    <row r="51" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ51" s="11" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
+    <row r="52" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ52" s="11" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+    <row r="53" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ53" s="11" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="11" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="11" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="11" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" s="11" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
+    <row r="55" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ55" s="7" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="56" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ56" s="10" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" s="11" t="s">
+    <row r="57" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ57" s="10" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" s="11" t="s">
+    <row r="58" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ58" s="10" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
+    <row r="59" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ59" s="10" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" s="11" t="s">
+    <row r="61" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ61" s="11" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" s="11" t="s">
+    <row r="62" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ62" s="11" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" s="11" t="s">
+    <row r="63" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ63" s="11" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" s="11" t="s">
+    <row r="64" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ64" s="11" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" s="11" t="s">
+    <row r="65" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ65" s="11" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="66" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ66" s="11" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="67" spans="62:62" x14ac:dyDescent="0.25">
+      <c r="BJ67" s="11" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" s="11"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" s="11" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" s="11" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" s="11" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" s="11" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" s="11" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A61" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" s="10"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" s="10" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" s="10" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" s="10" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A69" s="12" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A71" s="7" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A73" s="11" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A74" s="11" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A75" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A76" s="11" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A77" s="11" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A78" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A79" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A80" s="11" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A81" s="11" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A82" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A83" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A84" s="11" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A85" s="11" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A86" s="11" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A87" s="11" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A88" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A89" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A90" s="11"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A91" s="11" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A92" s="11" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A93" s="11" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A94" s="11" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A95" s="11" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A96" s="11" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A97" s="11"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A98" s="11" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A99" s="11" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A100" s="11" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A101" s="11" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A102" s="11" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A103" s="11" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A104" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A106" s="7" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A107" s="10"/>
-    </row>
-    <row r="108" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A108" s="8" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A109" s="8" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A110" s="8" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A112" s="9" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A116" s="12" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A118" s="7" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A120" s="11" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A121" s="11" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A122" s="11" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A123" s="11" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A124" s="11" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A125" s="11" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A126" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A127" s="11" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A128" s="11" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A129" s="11" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A130" s="11" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A131" s="11" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A132" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A133" s="11" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A134" s="11" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A135" s="11" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A136" s="11" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A137" s="11" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A138" s="11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A140" s="7" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A141" s="10"/>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A142" s="10" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A143" s="10" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A144" s="10" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A145" s="10" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A147" s="7" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A149" s="11" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A150" s="11" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A151" s="11" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A152" s="11" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A153" s="11" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A154" s="11" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A155" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A156" s="11" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A157" s="11" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A158" s="11" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A159" s="11" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A160" s="11" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A161" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A162" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A163" s="11"/>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A164" s="11" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A165" s="11" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A166" s="11" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A167" s="11" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A169" s="7" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A170" s="10"/>
-    </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A171" s="10" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A172" s="10" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A173" s="10" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A174" s="10" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A176" s="11" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A177" s="11" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A178" s="11" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A179" s="11" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A180" s="11" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A181" s="11" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A182" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A186" s="7"/>
-    </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A187" s="10"/>
-    </row>
-    <row r="188" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A188" s="8"/>
-    </row>
-    <row r="189" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A189" s="8"/>
-    </row>
-    <row r="190" spans="1:1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A190" s="8"/>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="7"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="10"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="8"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="8"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>